--- a/Excel/templates/dependants/DEPENDANTS_EXPORT_TEMPLATE.xlsx
+++ b/Excel/templates/dependants/DEPENDANTS_EXPORT_TEMPLATE.xlsx
@@ -2442,6 +2442,15 @@
   </si>
   <si>
     <t>NaN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lubumbashi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOANDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kisangani</t>
   </si>
 </sst>
 </file>
@@ -5923,18 +5932,10 @@
       <c r="A28" t="s" s="60">
         <v>0</v>
       </c>
-      <c r="B28" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Zamba",DEPENDANTS!$D$3:$D$725,"*Employ*")</f>
-      </c>
-      <c r="C28" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Zamba",DEPENDANTS!$D$3:$D$725,"*Conjoint*")</f>
-      </c>
-      <c r="D28" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Zamba",DEPENDANTS!$D$3:$D$725,"Enfant")</f>
-      </c>
-      <c r="E28" s="69">
-        <f>SUM(B28:D28)</f>
-      </c>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="69"/>
       <c r="F28" s="70"/>
       <c r="G28" s="44"/>
       <c r="H28" s="44"/>
@@ -5957,18 +5958,10 @@
       <c r="A29" t="s" s="60">
         <v>177</v>
       </c>
-      <c r="B29" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Kinshasa",DEPENDANTS!$D$3:$D$725,"*Employ*")</f>
-      </c>
-      <c r="C29" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Kinshasa",DEPENDANTS!$D$3:$D$725,"*Conjoint*")</f>
-      </c>
-      <c r="D29" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Kinshasa",DEPENDANTS!$D$3:$D$725,"Enfant")</f>
-      </c>
-      <c r="E29" s="69">
-        <f>SUM(B29:D29)</f>
-      </c>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="70"/>
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
@@ -5991,18 +5984,10 @@
       <c r="A30" t="s" s="60">
         <v>747</v>
       </c>
-      <c r="B30" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Lubudi",DEPENDANTS!$D$3:$D$725,"*Employ*")</f>
-      </c>
-      <c r="C30" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Lubudi",DEPENDANTS!$D$3:$D$725,"*Conjoint*")</f>
-      </c>
-      <c r="D30" s="61">
-        <f>COUNTIFS(DEPENDANTS!$G$3:$G$725,"Lubudi",DEPENDANTS!$D$3:$D$725,"Enfant")</f>
-      </c>
-      <c r="E30" s="69">
-        <f>SUM(B30:D30)</f>
-      </c>
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="70"/>
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
@@ -6023,20 +6008,12 @@
     </row>
     <row r="31" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s" s="64">
-        <v>753</v>
-      </c>
-      <c r="B31" s="65">
-        <f>SUM(B28:B30)</f>
-      </c>
-      <c r="C31" s="65">
-        <f>SUM(C28:C30)</f>
-      </c>
-      <c r="D31" s="65">
-        <f>SUM(D28:D30)</f>
-      </c>
-      <c r="E31" s="71">
-        <f>SUM(E28:E30)</f>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="71"/>
       <c r="F31" s="72"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
@@ -6056,7 +6033,9 @@
       <c r="V31" s="33"/>
     </row>
     <row r="32" spans="1:22" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
+      <c r="A32" t="s" s="2">
+        <v>801</v>
+      </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
       <c r="D32" s="29"/>
@@ -6081,7 +6060,7 @@
     </row>
     <row r="33" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s" s="67">
-        <v>754</v>
+        <v>802</v>
       </c>
       <c r="B33" s="54"/>
       <c r="C33" s="54"/>
@@ -6107,17 +6086,11 @@
     </row>
     <row r="34" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A34" t="s" s="57">
-        <v>207</v>
-      </c>
-      <c r="B34" t="s" s="58">
-        <v>755</v>
-      </c>
-      <c r="C34" t="s" s="58">
-        <v>756</v>
-      </c>
-      <c r="D34" t="s" s="58">
-        <v>4</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="59"/>
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
@@ -6138,18 +6111,10 @@
       <c r="V34" s="33"/>
     </row>
     <row r="35" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s" s="60">
-        <v>0</v>
-      </c>
-      <c r="B35" s="61">
-        <f ca="1">COUNTIFS(DEPENDANTS!$G$3:$G$725,"Zamba",DEPENDANTS!$I$3:$I$725,"&lt;=17")</f>
-      </c>
-      <c r="C35" s="61">
-        <f ca="1">COUNTIF(DEPENDANTS!$G$3:$G$725,"Zamba")-B35</f>
-      </c>
-      <c r="D35" s="62">
-        <f ca="1">SUM(B35:C35)</f>
-      </c>
+      <c r="A35" s="60"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="62"/>
       <c r="E35" s="63"/>
       <c r="F35" s="44"/>
       <c r="G35" s="44"/>
@@ -6171,17 +6136,11 @@
     </row>
     <row r="36" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s" s="60">
-        <v>177</v>
-      </c>
-      <c r="B36" s="61">
-        <f ca="1">COUNTIFS(DEPENDANTS!$G$3:$G$725,"Kinshasa",DEPENDANTS!$I$3:$I$725,"&lt;=17")</f>
-      </c>
-      <c r="C36" s="61">
-        <f ca="1">COUNTIF(DEPENDANTS!$G$3:$G$725,"Kinshasa")-B36</f>
-      </c>
-      <c r="D36" s="62">
-        <f ca="1">SUM(B36:C36)</f>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="63"/>
       <c r="F36" s="44"/>
       <c r="G36" s="44"/>
@@ -6203,16 +6162,16 @@
     </row>
     <row r="37" spans="1:6" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A37" t="s" s="60">
-        <v>747</v>
-      </c>
-      <c r="B37" s="61">
-        <f ca="1">COUNTIFS(DEPENDANTS!$G$3:$G$725,"Lubudi",DEPENDANTS!$I$3:$I$725,"&lt;=17")</f>
-      </c>
-      <c r="C37" s="61">
-        <f ca="1">COUNTIF(DEPENDANTS!$G$3:$G$725,"Lubudi")-B37</f>
-      </c>
-      <c r="D37" s="62">
-        <f ca="1">SUM(B37:C37)</f>
+        <v>207</v>
+      </c>
+      <c r="B37" t="s" s="61">
+        <v>755</v>
+      </c>
+      <c r="C37" t="s" s="61">
+        <v>756</v>
+      </c>
+      <c r="D37" t="s" s="62">
+        <v>4</v>
       </c>
       <c r="E37" s="63"/>
       <c r="F37" s="44"/>
@@ -6235,17 +6194,11 @@
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s" s="64">
-        <v>753</v>
-      </c>
-      <c r="B38" s="65">
-        <f ca="1">SUM(B35:B37)</f>
-      </c>
-      <c r="C38" s="65">
-        <f ca="1">SUM(C35:C37)</f>
-      </c>
-      <c r="D38" s="65">
-        <f ca="1">SUM(D35:D37)</f>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
       <c r="E38" s="66"/>
       <c r="F38" s="44"/>
       <c r="G38" s="44"/>
@@ -6264,6 +6217,102 @@
       <c r="T38" s="44"/>
       <c r="U38" s="33"/>
       <c r="V38" s="33"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/Excel/templates/dependants/DEPENDANTS_EXPORT_TEMPLATE.xlsx
+++ b/Excel/templates/dependants/DEPENDANTS_EXPORT_TEMPLATE.xlsx
@@ -16,15 +16,7 @@
     <sheet name="RESUME" sheetId="8" r:id="rId1"/>
     <sheet name="DEPENDANTS" sheetId="9" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DEPENDANTS!$A$2:$WVT$850</definedName>
-    <definedName name="_xlnm._FilterDatabase" hidden="1">'[1]CHECK DOCUMENTS BASE'!$B$3:$AD$3</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4732,19 +4724,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="CHECK DOCUMENTS BASE"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -7099,7 +7078,7 @@
         <v>30022</v>
       </c>
       <c r="I3" s="9">
-        <f ca="1" t="shared" ref="I3:I66" si="0">DATEDIF(H3,TODAY(),"Y")</f>
+        <f>DATEDIF(H3,TODAY(),"Y")</f>
       </c>
       <c r="J3" s="11">
         <v>1</v>
@@ -7141,7 +7120,7 @@
         <v>26225</v>
       </c>
       <c r="I4" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H4,TODAY(),"Y")</f>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="13"/>
@@ -7177,7 +7156,7 @@
         <v>40593</v>
       </c>
       <c r="I5" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H5,TODAY(),"Y")</f>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="13"/>
@@ -7213,7 +7192,7 @@
         <v>41303</v>
       </c>
       <c r="I6" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H6,TODAY(),"Y")</f>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="13"/>
@@ -7249,7 +7228,7 @@
         <v>34545</v>
       </c>
       <c r="I7" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H7,TODAY(),"Y")</f>
       </c>
       <c r="J7" s="12">
         <v>0</v>
@@ -7291,7 +7270,7 @@
         <v>27986</v>
       </c>
       <c r="I8" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H8,TODAY(),"Y")</f>
       </c>
       <c r="J8" s="14">
         <v>1</v>
@@ -7333,7 +7312,7 @@
         <v>37796</v>
       </c>
       <c r="I9" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H9,TODAY(),"Y")</f>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="13"/>
@@ -7369,7 +7348,7 @@
         <v>38460</v>
       </c>
       <c r="I10" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H10,TODAY(),"Y")</f>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="13"/>
@@ -7405,7 +7384,7 @@
         <v>39245</v>
       </c>
       <c r="I11" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H11,TODAY(),"Y")</f>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="13"/>
@@ -7441,7 +7420,7 @@
         <v>40155</v>
       </c>
       <c r="I12" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H12,TODAY(),"Y")</f>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="13"/>
@@ -7477,7 +7456,7 @@
         <v>24053</v>
       </c>
       <c r="I13" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H13,TODAY(),"Y")</f>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="13"/>
@@ -7513,7 +7492,7 @@
         <v>30328</v>
       </c>
       <c r="I14" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H14,TODAY(),"Y")</f>
       </c>
       <c r="J14" s="14">
         <v>1</v>
@@ -7555,7 +7534,7 @@
         <v>32408</v>
       </c>
       <c r="I15" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H15,TODAY(),"Y")</f>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="13"/>
@@ -7591,7 +7570,7 @@
         <v>42157</v>
       </c>
       <c r="I16" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H16,TODAY(),"Y")</f>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="13"/>
@@ -7627,7 +7606,7 @@
         <v>42604</v>
       </c>
       <c r="I17" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H17,TODAY(),"Y")</f>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="13"/>
@@ -7663,7 +7642,7 @@
         <v>44042</v>
       </c>
       <c r="I18" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H18,TODAY(),"Y")</f>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="13"/>
@@ -7699,7 +7678,7 @@
         <v>44596</v>
       </c>
       <c r="I19" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H19,TODAY(),"Y")</f>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="13"/>
@@ -7735,7 +7714,7 @@
         <v>46190</v>
       </c>
       <c r="I20" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H20,TODAY(),"Y")</f>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="11"/>
@@ -7773,7 +7752,7 @@
         <v>25208</v>
       </c>
       <c r="I21" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H21,TODAY(),"Y")</f>
       </c>
       <c r="J21" s="12">
         <v>1</v>
@@ -7815,7 +7794,7 @@
         <v>26155</v>
       </c>
       <c r="I22" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H22,TODAY(),"Y")</f>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="13"/>
@@ -7851,7 +7830,7 @@
         <v>40539</v>
       </c>
       <c r="I23" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H23,TODAY(),"Y")</f>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="13"/>
@@ -7887,7 +7866,7 @@
         <v>42141</v>
       </c>
       <c r="I24" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H24,TODAY(),"Y")</f>
       </c>
       <c r="J24" s="14"/>
       <c r="K24" s="13"/>
@@ -7923,7 +7902,7 @@
         <v>28799</v>
       </c>
       <c r="I25" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H25,TODAY(),"Y")</f>
       </c>
       <c r="J25" s="12">
         <v>1</v>
@@ -7965,7 +7944,7 @@
         <v>26402</v>
       </c>
       <c r="I26" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H26,TODAY(),"Y")</f>
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="13"/>
@@ -8001,7 +7980,7 @@
         <v>35405</v>
       </c>
       <c r="I27" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H27,TODAY(),"Y")</f>
       </c>
       <c r="J27" s="14">
         <v>0</v>
@@ -8043,7 +8022,7 @@
         <v>27917</v>
       </c>
       <c r="I28" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H28,TODAY(),"Y")</f>
       </c>
       <c r="J28" s="12">
         <v>1</v>
@@ -8085,7 +8064,7 @@
         <v>43293</v>
       </c>
       <c r="I29" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H29,TODAY(),"Y")</f>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="13"/>
@@ -8121,7 +8100,7 @@
         <v>31924</v>
       </c>
       <c r="I30" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H30,TODAY(),"Y")</f>
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="13"/>
@@ -8157,7 +8136,7 @@
         <v>44883</v>
       </c>
       <c r="I31" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H31,TODAY(),"Y")</f>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="11"/>
@@ -8193,7 +8172,7 @@
         <v>29768</v>
       </c>
       <c r="I32" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H32,TODAY(),"Y")</f>
       </c>
       <c r="J32" s="12">
         <v>1</v>
@@ -8235,7 +8214,7 @@
         <v>32609</v>
       </c>
       <c r="I33" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H33,TODAY(),"Y")</f>
       </c>
       <c r="J33" s="12"/>
       <c r="K33" s="13"/>
@@ -8271,7 +8250,7 @@
         <v>39183</v>
       </c>
       <c r="I34" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H34,TODAY(),"Y")</f>
       </c>
       <c r="J34" s="12"/>
       <c r="K34" s="13"/>
@@ -8307,7 +8286,7 @@
         <v>42160</v>
       </c>
       <c r="I35" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H35,TODAY(),"Y")</f>
       </c>
       <c r="J35" s="12"/>
       <c r="K35" s="13"/>
@@ -8343,7 +8322,7 @@
         <v>42771</v>
       </c>
       <c r="I36" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H36,TODAY(),"Y")</f>
       </c>
       <c r="J36" s="12"/>
       <c r="K36" s="13"/>
@@ -8379,7 +8358,7 @@
         <v>43855</v>
       </c>
       <c r="I37" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H37,TODAY(),"Y")</f>
       </c>
       <c r="J37" s="12"/>
       <c r="K37" s="13"/>
@@ -8415,7 +8394,7 @@
         <v>45743</v>
       </c>
       <c r="I38" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H38,TODAY(),"Y")</f>
       </c>
       <c r="J38" s="12"/>
       <c r="K38" s="13"/>
@@ -8451,7 +8430,7 @@
         <v>31542</v>
       </c>
       <c r="I39" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H39,TODAY(),"Y")</f>
       </c>
       <c r="J39" s="14">
         <v>0</v>
@@ -8493,7 +8472,7 @@
         <v>32197</v>
       </c>
       <c r="I40" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H40,TODAY(),"Y")</f>
       </c>
       <c r="J40" s="12">
         <v>1</v>
@@ -8535,7 +8514,7 @@
         <v>31981</v>
       </c>
       <c r="I41" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H41,TODAY(),"Y")</f>
       </c>
       <c r="J41" s="12"/>
       <c r="K41" s="13"/>
@@ -8571,7 +8550,7 @@
         <v>32273</v>
       </c>
       <c r="I42" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H42,TODAY(),"Y")</f>
       </c>
       <c r="J42" s="14">
         <v>0</v>
@@ -8613,7 +8592,7 @@
         <v>31105</v>
       </c>
       <c r="I43" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H43,TODAY(),"Y")</f>
       </c>
       <c r="J43" s="12">
         <v>1</v>
@@ -8655,7 +8634,7 @@
         <v>41336</v>
       </c>
       <c r="I44" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H44,TODAY(),"Y")</f>
       </c>
       <c r="J44" s="12"/>
       <c r="K44" s="13"/>
@@ -8691,7 +8670,7 @@
         <v>42388</v>
       </c>
       <c r="I45" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H45,TODAY(),"Y")</f>
       </c>
       <c r="J45" s="12"/>
       <c r="K45" s="13"/>
@@ -8727,7 +8706,7 @@
         <v>43192</v>
       </c>
       <c r="I46" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H46,TODAY(),"Y")</f>
       </c>
       <c r="J46" s="12"/>
       <c r="K46" s="13"/>
@@ -8763,7 +8742,7 @@
         <v>41714</v>
       </c>
       <c r="I47" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H47,TODAY(),"Y")</f>
       </c>
       <c r="J47" s="12"/>
       <c r="K47" s="13"/>
@@ -8799,7 +8778,7 @@
         <v>35206</v>
       </c>
       <c r="I48" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H48,TODAY(),"Y")</f>
       </c>
       <c r="J48" s="12"/>
       <c r="K48" s="13"/>
@@ -8835,7 +8814,7 @@
         <v>45099</v>
       </c>
       <c r="I49" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H49,TODAY(),"Y")</f>
       </c>
       <c r="J49" s="14"/>
       <c r="K49" s="11"/>
@@ -8871,7 +8850,7 @@
         <v>25275</v>
       </c>
       <c r="I50" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H50,TODAY(),"Y")</f>
       </c>
       <c r="J50" s="12">
         <v>1</v>
@@ -8913,7 +8892,7 @@
         <v>27452</v>
       </c>
       <c r="I51" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H51,TODAY(),"Y")</f>
       </c>
       <c r="J51" s="12"/>
       <c r="K51" s="13"/>
@@ -8949,7 +8928,7 @@
         <v>38340</v>
       </c>
       <c r="I52" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H52,TODAY(),"Y")</f>
       </c>
       <c r="J52" s="12"/>
       <c r="K52" s="13"/>
@@ -8985,7 +8964,7 @@
         <v>39544</v>
       </c>
       <c r="I53" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H53,TODAY(),"Y")</f>
       </c>
       <c r="J53" s="12"/>
       <c r="K53" s="13"/>
@@ -9021,7 +9000,7 @@
         <v>41307</v>
       </c>
       <c r="I54" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H54,TODAY(),"Y")</f>
       </c>
       <c r="J54" s="12"/>
       <c r="K54" s="13"/>
@@ -9057,7 +9036,7 @@
         <v>38315</v>
       </c>
       <c r="I55" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H55,TODAY(),"Y")</f>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="13"/>
@@ -9093,7 +9072,7 @@
         <v>36688</v>
       </c>
       <c r="I56" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H56,TODAY(),"Y")</f>
       </c>
       <c r="J56" s="12"/>
       <c r="K56" s="13"/>
@@ -9129,7 +9108,7 @@
         <v>37496</v>
       </c>
       <c r="I57" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H57,TODAY(),"Y")</f>
       </c>
       <c r="J57" s="14"/>
       <c r="K57" s="15"/>
@@ -9165,7 +9144,7 @@
         <v>33390</v>
       </c>
       <c r="I58" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H58,TODAY(),"Y")</f>
       </c>
       <c r="J58" s="12">
         <v>1</v>
@@ -9207,7 +9186,7 @@
         <v>34168</v>
       </c>
       <c r="I59" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H59,TODAY(),"Y")</f>
       </c>
       <c r="J59" s="14"/>
       <c r="K59" s="11"/>
@@ -9243,7 +9222,7 @@
         <v>34355</v>
       </c>
       <c r="I60" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H60,TODAY(),"Y")</f>
       </c>
       <c r="J60" s="12">
         <v>1</v>
@@ -9285,7 +9264,7 @@
         <v>29301</v>
       </c>
       <c r="I61" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H61,TODAY(),"Y")</f>
       </c>
       <c r="J61" s="12"/>
       <c r="K61" s="13"/>
@@ -9321,7 +9300,7 @@
         <v>40873</v>
       </c>
       <c r="I62" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H62,TODAY(),"Y")</f>
       </c>
       <c r="J62" s="12"/>
       <c r="K62" s="13"/>
@@ -9357,7 +9336,7 @@
         <v>41422</v>
       </c>
       <c r="I63" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H63,TODAY(),"Y")</f>
       </c>
       <c r="J63" s="12"/>
       <c r="K63" s="13"/>
@@ -9393,7 +9372,7 @@
         <v>45084</v>
       </c>
       <c r="I64" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H64,TODAY(),"Y")</f>
       </c>
       <c r="J64" s="12"/>
       <c r="K64" s="13"/>
@@ -9429,7 +9408,7 @@
         <v>45806</v>
       </c>
       <c r="I65" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H65,TODAY(),"Y")</f>
       </c>
       <c r="J65" s="14"/>
       <c r="K65" s="11"/>
@@ -9465,7 +9444,7 @@
         <v>26447</v>
       </c>
       <c r="I66" s="9">
-        <f ca="1" t="shared" si="0"/>
+        <f>DATEDIF(H66,TODAY(),"Y")</f>
       </c>
       <c r="J66" s="12">
         <v>1</v>
@@ -9507,7 +9486,7 @@
         <v>31911</v>
       </c>
       <c r="I67" s="9">
-        <f ca="1" t="shared" ref="I67:I130" si="1">DATEDIF(H67,TODAY(),"Y")</f>
+        <f>DATEDIF(H67,TODAY(),"Y")</f>
       </c>
       <c r="J67" s="12"/>
       <c r="K67" s="13"/>
@@ -9543,7 +9522,7 @@
         <v>43248</v>
       </c>
       <c r="I68" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H68,TODAY(),"Y")</f>
       </c>
       <c r="J68" s="12"/>
       <c r="K68" s="13"/>
@@ -9579,7 +9558,7 @@
         <v>39539</v>
       </c>
       <c r="I69" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H69,TODAY(),"Y")</f>
       </c>
       <c r="J69" s="12"/>
       <c r="K69" s="13"/>
@@ -9615,7 +9594,7 @@
         <v>44274</v>
       </c>
       <c r="I70" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H70,TODAY(),"Y")</f>
       </c>
       <c r="J70" s="12"/>
       <c r="K70" s="13"/>
@@ -9651,7 +9630,7 @@
         <v>40370</v>
       </c>
       <c r="I71" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H71,TODAY(),"Y")</f>
       </c>
       <c r="J71" s="14"/>
       <c r="K71" s="11"/>
@@ -9687,7 +9666,7 @@
         <v>28178</v>
       </c>
       <c r="I72" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H72,TODAY(),"Y")</f>
       </c>
       <c r="J72" s="12">
         <v>1</v>
@@ -9729,7 +9708,7 @@
         <v>29138</v>
       </c>
       <c r="I73" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H73,TODAY(),"Y")</f>
       </c>
       <c r="J73" s="12"/>
       <c r="K73" s="13"/>
@@ -9765,7 +9744,7 @@
         <v>38292</v>
       </c>
       <c r="I74" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H74,TODAY(),"Y")</f>
       </c>
       <c r="J74" s="12"/>
       <c r="K74" s="13"/>
@@ -9801,7 +9780,7 @@
         <v>40481</v>
       </c>
       <c r="I75" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H75,TODAY(),"Y")</f>
       </c>
       <c r="J75" s="12"/>
       <c r="K75" s="13"/>
@@ -9837,7 +9816,7 @@
         <v>41106</v>
       </c>
       <c r="I76" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H76,TODAY(),"Y")</f>
       </c>
       <c r="J76" s="12"/>
       <c r="K76" s="13"/>
@@ -9873,7 +9852,7 @@
         <v>42130</v>
       </c>
       <c r="I77" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H77,TODAY(),"Y")</f>
       </c>
       <c r="J77" s="14"/>
       <c r="K77" s="11"/>
@@ -9909,7 +9888,7 @@
         <v>32582</v>
       </c>
       <c r="I78" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H78,TODAY(),"Y")</f>
       </c>
       <c r="J78" s="12">
         <v>1</v>
@@ -9951,7 +9930,7 @@
         <v>34594</v>
       </c>
       <c r="I79" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H79,TODAY(),"Y")</f>
       </c>
       <c r="J79" s="12"/>
       <c r="K79" s="13"/>
@@ -9987,7 +9966,7 @@
         <v>41779</v>
       </c>
       <c r="I80" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H80,TODAY(),"Y")</f>
       </c>
       <c r="J80" s="12"/>
       <c r="K80" s="13"/>
@@ -10023,7 +10002,7 @@
         <v>44532</v>
       </c>
       <c r="I81" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H81,TODAY(),"Y")</f>
       </c>
       <c r="J81" s="12"/>
       <c r="K81" s="13"/>
@@ -10059,7 +10038,7 @@
         <v>45360</v>
       </c>
       <c r="I82" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H82,TODAY(),"Y")</f>
       </c>
       <c r="J82" s="14"/>
       <c r="K82" s="11"/>
@@ -10095,7 +10074,7 @@
         <v>32706</v>
       </c>
       <c r="I83" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H83,TODAY(),"Y")</f>
       </c>
       <c r="J83" s="12">
         <v>1</v>
@@ -10137,7 +10116,7 @@
         <v>34931</v>
       </c>
       <c r="I84" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H84,TODAY(),"Y")</f>
       </c>
       <c r="J84" s="12"/>
       <c r="K84" s="13"/>
@@ -10173,7 +10152,7 @@
         <v>43980</v>
       </c>
       <c r="I85" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H85,TODAY(),"Y")</f>
       </c>
       <c r="J85" s="12"/>
       <c r="K85" s="13"/>
@@ -10209,7 +10188,7 @@
         <v>44560</v>
       </c>
       <c r="I86" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H86,TODAY(),"Y")</f>
       </c>
       <c r="J86" s="12"/>
       <c r="K86" s="13"/>
@@ -10245,7 +10224,7 @@
         <v>44948</v>
       </c>
       <c r="I87" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H87,TODAY(),"Y")</f>
       </c>
       <c r="J87" s="14"/>
       <c r="K87" s="11"/>
@@ -10281,7 +10260,7 @@
         <v>29891</v>
       </c>
       <c r="I88" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H88,TODAY(),"Y")</f>
       </c>
       <c r="J88" s="12">
         <v>1</v>
@@ -10323,7 +10302,7 @@
         <v>30426</v>
       </c>
       <c r="I89" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H89,TODAY(),"Y")</f>
       </c>
       <c r="J89" s="12"/>
       <c r="K89" s="13"/>
@@ -10359,7 +10338,7 @@
         <v>40736</v>
       </c>
       <c r="I90" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H90,TODAY(),"Y")</f>
       </c>
       <c r="J90" s="12"/>
       <c r="K90" s="13"/>
@@ -10395,7 +10374,7 @@
         <v>41377</v>
       </c>
       <c r="I91" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H91,TODAY(),"Y")</f>
       </c>
       <c r="J91" s="14"/>
       <c r="K91" s="11"/>
@@ -10431,7 +10410,7 @@
         <v>30794</v>
       </c>
       <c r="I92" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H92,TODAY(),"Y")</f>
       </c>
       <c r="J92" s="12">
         <v>1</v>
@@ -10473,7 +10452,7 @@
         <v>36289</v>
       </c>
       <c r="I93" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H93,TODAY(),"Y")</f>
       </c>
       <c r="J93" s="12"/>
       <c r="K93" s="13"/>
@@ -10509,7 +10488,7 @@
         <v>39000</v>
       </c>
       <c r="I94" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H94,TODAY(),"Y")</f>
       </c>
       <c r="J94" s="12"/>
       <c r="K94" s="13"/>
@@ -10545,7 +10524,7 @@
         <v>43911</v>
       </c>
       <c r="I95" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H95,TODAY(),"Y")</f>
       </c>
       <c r="J95" s="12"/>
       <c r="K95" s="13"/>
@@ -10581,7 +10560,7 @@
         <v>43911</v>
       </c>
       <c r="I96" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H96,TODAY(),"Y")</f>
       </c>
       <c r="J96" s="12"/>
       <c r="K96" s="13"/>
@@ -10617,7 +10596,7 @@
         <v>44541</v>
       </c>
       <c r="I97" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H97,TODAY(),"Y")</f>
       </c>
       <c r="J97" s="12"/>
       <c r="K97" s="13"/>
@@ -10653,7 +10632,7 @@
         <v>45482</v>
       </c>
       <c r="I98" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H98,TODAY(),"Y")</f>
       </c>
       <c r="J98" s="14"/>
       <c r="K98" s="11"/>
@@ -10689,7 +10668,7 @@
         <v>31855</v>
       </c>
       <c r="I99" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H99,TODAY(),"Y")</f>
       </c>
       <c r="J99" s="12">
         <v>1</v>
@@ -10731,7 +10710,7 @@
         <v>35011</v>
       </c>
       <c r="I100" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H100,TODAY(),"Y")</f>
       </c>
       <c r="J100" s="12"/>
       <c r="K100" s="13"/>
@@ -10767,7 +10746,7 @@
         <v>42635</v>
       </c>
       <c r="I101" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H101,TODAY(),"Y")</f>
       </c>
       <c r="J101" s="12"/>
       <c r="K101" s="13"/>
@@ -10803,7 +10782,7 @@
         <v>43192</v>
       </c>
       <c r="I102" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H102,TODAY(),"Y")</f>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="13"/>
@@ -10839,7 +10818,7 @@
         <v>44986</v>
       </c>
       <c r="I103" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H103,TODAY(),"Y")</f>
       </c>
       <c r="J103" s="12"/>
       <c r="K103" s="13"/>
@@ -10875,7 +10854,7 @@
         <v>45989</v>
       </c>
       <c r="I104" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H104,TODAY(),"Y")</f>
       </c>
       <c r="J104" s="14"/>
       <c r="K104" s="11"/>
@@ -10911,7 +10890,7 @@
         <v>27917</v>
       </c>
       <c r="I105" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H105,TODAY(),"Y")</f>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -10953,7 +10932,7 @@
         <v>33571</v>
       </c>
       <c r="I106" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H106,TODAY(),"Y")</f>
       </c>
       <c r="J106" s="12"/>
       <c r="K106" s="13"/>
@@ -10989,7 +10968,7 @@
         <v>40412</v>
       </c>
       <c r="I107" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H107,TODAY(),"Y")</f>
       </c>
       <c r="J107" s="12"/>
       <c r="K107" s="13"/>
@@ -11025,7 +11004,7 @@
         <v>42242</v>
       </c>
       <c r="I108" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H108,TODAY(),"Y")</f>
       </c>
       <c r="J108" s="12"/>
       <c r="K108" s="13"/>
@@ -11061,7 +11040,7 @@
         <v>42877</v>
       </c>
       <c r="I109" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H109,TODAY(),"Y")</f>
       </c>
       <c r="J109" s="12"/>
       <c r="K109" s="13"/>
@@ -11097,7 +11076,7 @@
         <v>43591</v>
       </c>
       <c r="I110" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H110,TODAY(),"Y")</f>
       </c>
       <c r="J110" s="12"/>
       <c r="K110" s="13"/>
@@ -11133,7 +11112,7 @@
         <v>45727</v>
       </c>
       <c r="I111" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H111,TODAY(),"Y")</f>
       </c>
       <c r="J111" s="14"/>
       <c r="K111" s="11"/>
@@ -11169,7 +11148,7 @@
         <v>32392</v>
       </c>
       <c r="I112" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H112,TODAY(),"Y")</f>
       </c>
       <c r="J112" s="12">
         <v>1</v>
@@ -11211,7 +11190,7 @@
         <v>33188</v>
       </c>
       <c r="I113" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H113,TODAY(),"Y")</f>
       </c>
       <c r="J113" s="12"/>
       <c r="K113" s="13"/>
@@ -11247,7 +11226,7 @@
         <v>44114</v>
       </c>
       <c r="I114" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H114,TODAY(),"Y")</f>
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="13"/>
@@ -11283,7 +11262,7 @@
         <v>44701</v>
       </c>
       <c r="I115" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H115,TODAY(),"Y")</f>
       </c>
       <c r="J115" s="14"/>
       <c r="K115" s="15"/>
@@ -11319,7 +11298,7 @@
         <v>31255</v>
       </c>
       <c r="I116" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H116,TODAY(),"Y")</f>
       </c>
       <c r="J116" s="12">
         <v>1</v>
@@ -11361,7 +11340,7 @@
         <v>33654</v>
       </c>
       <c r="I117" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H117,TODAY(),"Y")</f>
       </c>
       <c r="J117" s="12"/>
       <c r="K117" s="13"/>
@@ -11397,7 +11376,7 @@
         <v>46100</v>
       </c>
       <c r="I118" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H118,TODAY(),"Y")</f>
       </c>
       <c r="J118" s="12"/>
       <c r="K118" s="11"/>
@@ -11433,7 +11412,7 @@
         <v>30115</v>
       </c>
       <c r="I119" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H119,TODAY(),"Y")</f>
       </c>
       <c r="J119" s="12">
         <v>0</v>
@@ -11475,7 +11454,7 @@
         <v>40087</v>
       </c>
       <c r="I120" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H120,TODAY(),"Y")</f>
       </c>
       <c r="J120" s="14"/>
       <c r="K120" s="11"/>
@@ -11511,7 +11490,7 @@
         <v>31638</v>
       </c>
       <c r="I121" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H121,TODAY(),"Y")</f>
       </c>
       <c r="J121" s="12">
         <v>1</v>
@@ -11553,7 +11532,7 @@
         <v>33537</v>
       </c>
       <c r="I122" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H122,TODAY(),"Y")</f>
       </c>
       <c r="J122" s="12"/>
       <c r="K122" s="13"/>
@@ -11589,7 +11568,7 @@
         <v>42382</v>
       </c>
       <c r="I123" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H123,TODAY(),"Y")</f>
       </c>
       <c r="J123" s="12"/>
       <c r="K123" s="13"/>
@@ -11625,7 +11604,7 @@
         <v>43260</v>
       </c>
       <c r="I124" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H124,TODAY(),"Y")</f>
       </c>
       <c r="J124" s="12"/>
       <c r="K124" s="13"/>
@@ -11661,7 +11640,7 @@
         <v>43717</v>
       </c>
       <c r="I125" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H125,TODAY(),"Y")</f>
       </c>
       <c r="J125" s="12"/>
       <c r="K125" s="13"/>
@@ -11697,7 +11676,7 @@
         <v>45090</v>
       </c>
       <c r="I126" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H126,TODAY(),"Y")</f>
       </c>
       <c r="J126" s="14"/>
       <c r="K126" s="11"/>
@@ -11733,7 +11712,7 @@
         <v>33504</v>
       </c>
       <c r="I127" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H127,TODAY(),"Y")</f>
       </c>
       <c r="J127" s="12">
         <v>1</v>
@@ -11775,7 +11754,7 @@
         <v>34229</v>
       </c>
       <c r="I128" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H128,TODAY(),"Y")</f>
       </c>
       <c r="J128" s="12"/>
       <c r="K128" s="13"/>
@@ -11811,7 +11790,7 @@
         <v>43628</v>
       </c>
       <c r="I129" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H129,TODAY(),"Y")</f>
       </c>
       <c r="J129" s="12"/>
       <c r="K129" s="13"/>
@@ -11847,7 +11826,7 @@
         <v>44859</v>
       </c>
       <c r="I130" s="9">
-        <f ca="1" t="shared" si="1"/>
+        <f>DATEDIF(H130,TODAY(),"Y")</f>
       </c>
       <c r="J130" s="14"/>
       <c r="K130" s="15"/>
@@ -11883,7 +11862,7 @@
         <v>46019</v>
       </c>
       <c r="I131" s="9">
-        <f ca="1" t="shared" ref="I131:I194" si="2">DATEDIF(H131,TODAY(),"Y")</f>
+        <f>DATEDIF(H131,TODAY(),"Y")</f>
       </c>
       <c r="J131" s="12"/>
       <c r="K131" s="13"/>
@@ -11921,7 +11900,7 @@
         <v>32229</v>
       </c>
       <c r="I132" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H132,TODAY(),"Y")</f>
       </c>
       <c r="J132" s="14">
         <v>1</v>
@@ -11963,7 +11942,7 @@
         <v>36345</v>
       </c>
       <c r="I133" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H133,TODAY(),"Y")</f>
       </c>
       <c r="J133" s="12"/>
       <c r="K133" s="13"/>
@@ -11999,7 +11978,7 @@
         <v>46147</v>
       </c>
       <c r="I134" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H134,TODAY(),"Y")</f>
       </c>
       <c r="J134" s="12"/>
       <c r="K134" s="13"/>
@@ -12037,7 +12016,7 @@
         <v>31917</v>
       </c>
       <c r="I135" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H135,TODAY(),"Y")</f>
       </c>
       <c r="J135" s="12">
         <v>1</v>
@@ -12079,7 +12058,7 @@
         <v>33831</v>
       </c>
       <c r="I136" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H136,TODAY(),"Y")</f>
       </c>
       <c r="J136" s="14"/>
       <c r="K136" s="15"/>
@@ -12115,7 +12094,7 @@
         <v>44624</v>
       </c>
       <c r="I137" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H137,TODAY(),"Y")</f>
       </c>
       <c r="J137" s="12"/>
       <c r="K137" s="13"/>
@@ -12151,7 +12130,7 @@
         <v>45316</v>
       </c>
       <c r="I138" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H138,TODAY(),"Y")</f>
       </c>
       <c r="J138" s="12"/>
       <c r="K138" s="13"/>
@@ -12187,7 +12166,7 @@
         <v>33256</v>
       </c>
       <c r="I139" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H139,TODAY(),"Y")</f>
       </c>
       <c r="J139" s="14">
         <v>1</v>
@@ -12229,7 +12208,7 @@
         <v>36146</v>
       </c>
       <c r="I140" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H140,TODAY(),"Y")</f>
       </c>
       <c r="J140" s="12"/>
       <c r="K140" s="13"/>
@@ -12265,7 +12244,7 @@
         <v>46191</v>
       </c>
       <c r="I141" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H141,TODAY(),"Y")</f>
       </c>
       <c r="J141" s="12"/>
       <c r="K141" s="13"/>
@@ -12305,7 +12284,7 @@
         <v>32874</v>
       </c>
       <c r="I142" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H142,TODAY(),"Y")</f>
       </c>
       <c r="J142" s="12">
         <v>0</v>
@@ -12347,7 +12326,7 @@
         <v>30130</v>
       </c>
       <c r="I143" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H143,TODAY(),"Y")</f>
       </c>
       <c r="J143" s="12">
         <v>1</v>
@@ -12389,7 +12368,7 @@
         <v>28436</v>
       </c>
       <c r="I144" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H144,TODAY(),"Y")</f>
       </c>
       <c r="J144" s="12"/>
       <c r="K144" s="13"/>
@@ -12425,7 +12404,7 @@
         <v>38318</v>
       </c>
       <c r="I145" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H145,TODAY(),"Y")</f>
       </c>
       <c r="J145" s="14"/>
       <c r="K145" s="11"/>
@@ -12461,7 +12440,7 @@
         <v>42148</v>
       </c>
       <c r="I146" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H146,TODAY(),"Y")</f>
       </c>
       <c r="J146" s="12"/>
       <c r="K146" s="13"/>
@@ -12497,7 +12476,7 @@
         <v>42696</v>
       </c>
       <c r="I147" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H147,TODAY(),"Y")</f>
       </c>
       <c r="J147" s="12"/>
       <c r="K147" s="13"/>
@@ -12535,7 +12514,7 @@
         <v>40217</v>
       </c>
       <c r="I148" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H148,TODAY(),"Y")</f>
       </c>
       <c r="J148" s="12"/>
       <c r="K148" s="13"/>
@@ -12573,7 +12552,7 @@
         <v>34084</v>
       </c>
       <c r="I149" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H149,TODAY(),"Y")</f>
       </c>
       <c r="J149" s="14">
         <v>1</v>
@@ -12615,7 +12594,7 @@
         <v>38874</v>
       </c>
       <c r="I150" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H150,TODAY(),"Y")</f>
       </c>
       <c r="J150" s="12"/>
       <c r="K150" s="13"/>
@@ -12651,7 +12630,7 @@
         <v>31684</v>
       </c>
       <c r="I151" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H151,TODAY(),"Y")</f>
       </c>
       <c r="J151" s="12"/>
       <c r="K151" s="13"/>
@@ -12687,7 +12666,7 @@
         <v>45857</v>
       </c>
       <c r="I152" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H152,TODAY(),"Y")</f>
       </c>
       <c r="J152" s="12"/>
       <c r="K152" s="13"/>
@@ -12723,7 +12702,7 @@
         <v>28062</v>
       </c>
       <c r="I153" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H153,TODAY(),"Y")</f>
       </c>
       <c r="J153" s="12">
         <v>1</v>
@@ -12765,7 +12744,7 @@
         <v>31038</v>
       </c>
       <c r="I154" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H154,TODAY(),"Y")</f>
       </c>
       <c r="J154" s="12"/>
       <c r="K154" s="13"/>
@@ -12801,7 +12780,7 @@
         <v>36986</v>
       </c>
       <c r="I155" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H155,TODAY(),"Y")</f>
       </c>
       <c r="J155" s="12"/>
       <c r="K155" s="13"/>
@@ -12837,7 +12816,7 @@
         <v>37766</v>
       </c>
       <c r="I156" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H156,TODAY(),"Y")</f>
       </c>
       <c r="J156" s="12"/>
       <c r="K156" s="13"/>
@@ -12873,7 +12852,7 @@
         <v>40879</v>
       </c>
       <c r="I157" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H157,TODAY(),"Y")</f>
       </c>
       <c r="J157" s="12"/>
       <c r="K157" s="13"/>
@@ -12909,7 +12888,7 @@
         <v>44393</v>
       </c>
       <c r="I158" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H158,TODAY(),"Y")</f>
       </c>
       <c r="J158" s="14"/>
       <c r="K158" s="11"/>
@@ -12945,7 +12924,7 @@
         <v>38472</v>
       </c>
       <c r="I159" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H159,TODAY(),"Y")</f>
       </c>
       <c r="J159" s="12"/>
       <c r="K159" s="13"/>
@@ -12981,7 +12960,7 @@
         <v>45237</v>
       </c>
       <c r="I160" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H160,TODAY(),"Y")</f>
       </c>
       <c r="J160" s="12"/>
       <c r="K160" s="13"/>
@@ -13017,7 +12996,7 @@
         <v>32543</v>
       </c>
       <c r="I161" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H161,TODAY(),"Y")</f>
       </c>
       <c r="J161" s="12">
         <v>0</v>
@@ -13059,7 +13038,7 @@
         <v>30536</v>
       </c>
       <c r="I162" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H162,TODAY(),"Y")</f>
       </c>
       <c r="J162" s="12">
         <v>1</v>
@@ -13101,7 +13080,7 @@
         <v>32669</v>
       </c>
       <c r="I163" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H163,TODAY(),"Y")</f>
       </c>
       <c r="J163" s="12"/>
       <c r="K163" s="13"/>
@@ -13137,7 +13116,7 @@
         <v>41548</v>
       </c>
       <c r="I164" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H164,TODAY(),"Y")</f>
       </c>
       <c r="J164" s="12"/>
       <c r="K164" s="13"/>
@@ -13173,7 +13152,7 @@
         <v>42404</v>
       </c>
       <c r="I165" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H165,TODAY(),"Y")</f>
       </c>
       <c r="J165" s="12"/>
       <c r="K165" s="13"/>
@@ -13209,7 +13188,7 @@
         <v>40953</v>
       </c>
       <c r="I166" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H166,TODAY(),"Y")</f>
       </c>
       <c r="J166" s="12"/>
       <c r="K166" s="13"/>
@@ -13245,7 +13224,7 @@
         <v>43654</v>
       </c>
       <c r="I167" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H167,TODAY(),"Y")</f>
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="11"/>
@@ -13281,7 +13260,7 @@
         <v>37778</v>
       </c>
       <c r="I168" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H168,TODAY(),"Y")</f>
       </c>
       <c r="J168" s="12"/>
       <c r="K168" s="13"/>
@@ -13317,7 +13296,7 @@
         <v>44585</v>
       </c>
       <c r="I169" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H169,TODAY(),"Y")</f>
       </c>
       <c r="J169" s="12"/>
       <c r="K169" s="13"/>
@@ -13353,7 +13332,7 @@
         <v>45882</v>
       </c>
       <c r="I170" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H170,TODAY(),"Y")</f>
       </c>
       <c r="J170" s="12"/>
       <c r="K170" s="13"/>
@@ -13389,7 +13368,7 @@
         <v>25330</v>
       </c>
       <c r="I171" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H171,TODAY(),"Y")</f>
       </c>
       <c r="J171" s="12">
         <v>1</v>
@@ -13431,7 +13410,7 @@
         <v>27325</v>
       </c>
       <c r="I172" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H172,TODAY(),"Y")</f>
       </c>
       <c r="J172" s="14"/>
       <c r="K172" s="15"/>
@@ -13467,7 +13446,7 @@
         <v>38165</v>
       </c>
       <c r="I173" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H173,TODAY(),"Y")</f>
       </c>
       <c r="J173" s="12"/>
       <c r="K173" s="13"/>
@@ -13503,7 +13482,7 @@
         <v>38165</v>
       </c>
       <c r="I174" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H174,TODAY(),"Y")</f>
       </c>
       <c r="J174" s="12"/>
       <c r="K174" s="13"/>
@@ -13539,7 +13518,7 @@
         <v>38165</v>
       </c>
       <c r="I175" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H175,TODAY(),"Y")</f>
       </c>
       <c r="J175" s="12"/>
       <c r="K175" s="13"/>
@@ -13575,7 +13554,7 @@
         <v>23836</v>
       </c>
       <c r="I176" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H176,TODAY(),"Y")</f>
       </c>
       <c r="J176" s="14">
         <v>1</v>
@@ -13617,7 +13596,7 @@
         <v>28486</v>
       </c>
       <c r="I177" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H177,TODAY(),"Y")</f>
       </c>
       <c r="J177" s="12"/>
       <c r="K177" s="13"/>
@@ -13653,7 +13632,7 @@
         <v>31685</v>
       </c>
       <c r="I178" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H178,TODAY(),"Y")</f>
       </c>
       <c r="J178" s="12">
         <v>0</v>
@@ -13695,7 +13674,7 @@
         <v>33139</v>
       </c>
       <c r="I179" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H179,TODAY(),"Y")</f>
       </c>
       <c r="J179" s="12">
         <v>0</v>
@@ -13737,7 +13716,7 @@
         <v>32111</v>
       </c>
       <c r="I180" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H180,TODAY(),"Y")</f>
       </c>
       <c r="J180" s="14">
         <v>1</v>
@@ -13779,7 +13758,7 @@
         <v>33801</v>
       </c>
       <c r="I181" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H181,TODAY(),"Y")</f>
       </c>
       <c r="J181" s="12"/>
       <c r="K181" s="13"/>
@@ -13815,7 +13794,7 @@
         <v>45378</v>
       </c>
       <c r="I182" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H182,TODAY(),"Y")</f>
       </c>
       <c r="J182" s="12"/>
       <c r="K182" s="13"/>
@@ -13851,7 +13830,7 @@
         <v>45884</v>
       </c>
       <c r="I183" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H183,TODAY(),"Y")</f>
       </c>
       <c r="J183" s="12"/>
       <c r="K183" s="13"/>
@@ -13887,7 +13866,7 @@
         <v>30277</v>
       </c>
       <c r="I184" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H184,TODAY(),"Y")</f>
       </c>
       <c r="J184" s="12">
         <v>1</v>
@@ -13929,7 +13908,7 @@
         <v>30779</v>
       </c>
       <c r="I185" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H185,TODAY(),"Y")</f>
       </c>
       <c r="J185" s="12"/>
       <c r="K185" s="13"/>
@@ -13965,7 +13944,7 @@
         <v>41374</v>
       </c>
       <c r="I186" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H186,TODAY(),"Y")</f>
       </c>
       <c r="J186" s="12"/>
       <c r="K186" s="13"/>
@@ -14001,7 +13980,7 @@
         <v>42706</v>
       </c>
       <c r="I187" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H187,TODAY(),"Y")</f>
       </c>
       <c r="J187" s="14"/>
       <c r="K187" s="15"/>
@@ -14037,7 +14016,7 @@
         <v>43111</v>
       </c>
       <c r="I188" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H188,TODAY(),"Y")</f>
       </c>
       <c r="J188" s="12"/>
       <c r="K188" s="13"/>
@@ -14073,7 +14052,7 @@
         <v>44128</v>
       </c>
       <c r="I189" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H189,TODAY(),"Y")</f>
       </c>
       <c r="J189" s="14"/>
       <c r="K189" s="11"/>
@@ -14109,7 +14088,7 @@
         <v>45195</v>
       </c>
       <c r="I190" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H190,TODAY(),"Y")</f>
       </c>
       <c r="J190" s="12"/>
       <c r="K190" s="13"/>
@@ -14145,7 +14124,7 @@
         <v>31303</v>
       </c>
       <c r="I191" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H191,TODAY(),"Y")</f>
       </c>
       <c r="J191" s="12">
         <v>1</v>
@@ -14187,7 +14166,7 @@
         <v>34674</v>
       </c>
       <c r="I192" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H192,TODAY(),"Y")</f>
       </c>
       <c r="J192" s="12"/>
       <c r="K192" s="13"/>
@@ -14223,7 +14202,7 @@
         <v>30372</v>
       </c>
       <c r="I193" s="9">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H193,TODAY(),"Y")</f>
       </c>
       <c r="J193" s="14">
         <v>1</v>
@@ -14265,7 +14244,7 @@
         <v>30415</v>
       </c>
       <c r="I194" s="10">
-        <f ca="1" t="shared" si="2"/>
+        <f>DATEDIF(H194,TODAY(),"Y")</f>
       </c>
       <c r="J194" s="12"/>
       <c r="K194" s="13"/>
@@ -14301,7 +14280,7 @@
         <v>42834</v>
       </c>
       <c r="I195" s="9">
-        <f ca="1" t="shared" ref="I195:I258" si="3">DATEDIF(H195,TODAY(),"Y")</f>
+        <f>DATEDIF(H195,TODAY(),"Y")</f>
       </c>
       <c r="J195" s="12"/>
       <c r="K195" s="13"/>
@@ -14337,7 +14316,7 @@
         <v>43202</v>
       </c>
       <c r="I196" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H196,TODAY(),"Y")</f>
       </c>
       <c r="J196" s="12"/>
       <c r="K196" s="13"/>
@@ -14373,7 +14352,7 @@
         <v>28108</v>
       </c>
       <c r="I197" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H197,TODAY(),"Y")</f>
       </c>
       <c r="J197" s="12">
         <v>1</v>
@@ -14415,7 +14394,7 @@
         <v>30543</v>
       </c>
       <c r="I198" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H198,TODAY(),"Y")</f>
       </c>
       <c r="J198" s="12"/>
       <c r="K198" s="13"/>
@@ -14451,7 +14430,7 @@
         <v>38820</v>
       </c>
       <c r="I199" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H199,TODAY(),"Y")</f>
       </c>
       <c r="J199" s="12"/>
       <c r="K199" s="13"/>
@@ -14487,7 +14466,7 @@
         <v>39294</v>
       </c>
       <c r="I200" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H200,TODAY(),"Y")</f>
       </c>
       <c r="J200" s="14"/>
       <c r="K200" s="11"/>
@@ -14523,7 +14502,7 @@
         <v>40579</v>
       </c>
       <c r="I201" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H201,TODAY(),"Y")</f>
       </c>
       <c r="J201" s="12"/>
       <c r="K201" s="13"/>
@@ -14559,7 +14538,7 @@
         <v>42555</v>
       </c>
       <c r="I202" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H202,TODAY(),"Y")</f>
       </c>
       <c r="J202" s="12"/>
       <c r="K202" s="13"/>
@@ -14595,7 +14574,7 @@
         <v>43869</v>
       </c>
       <c r="I203" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H203,TODAY(),"Y")</f>
       </c>
       <c r="J203" s="12"/>
       <c r="K203" s="13"/>
@@ -14631,7 +14610,7 @@
         <v>27917</v>
       </c>
       <c r="I204" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H204,TODAY(),"Y")</f>
       </c>
       <c r="J204" s="12">
         <v>1</v>
@@ -14673,7 +14652,7 @@
         <v>29414</v>
       </c>
       <c r="I205" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H205,TODAY(),"Y")</f>
       </c>
       <c r="J205" s="12"/>
       <c r="K205" s="13"/>
@@ -14709,7 +14688,7 @@
         <v>38172</v>
       </c>
       <c r="I206" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H206,TODAY(),"Y")</f>
       </c>
       <c r="J206" s="12"/>
       <c r="K206" s="13"/>
@@ -14745,7 +14724,7 @@
         <v>38172</v>
       </c>
       <c r="I207" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H207,TODAY(),"Y")</f>
       </c>
       <c r="J207" s="12"/>
       <c r="K207" s="13"/>
@@ -14781,7 +14760,7 @@
         <v>39149</v>
       </c>
       <c r="I208" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H208,TODAY(),"Y")</f>
       </c>
       <c r="J208" s="12"/>
       <c r="K208" s="13"/>
@@ -14817,7 +14796,7 @@
         <v>40500</v>
       </c>
       <c r="I209" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H209,TODAY(),"Y")</f>
       </c>
       <c r="J209" s="12"/>
       <c r="K209" s="13"/>
@@ -14853,7 +14832,7 @@
         <v>41038</v>
       </c>
       <c r="I210" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H210,TODAY(),"Y")</f>
       </c>
       <c r="J210" s="14"/>
       <c r="K210" s="11"/>
@@ -14889,7 +14868,7 @@
         <v>41814</v>
       </c>
       <c r="I211" s="10">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H211,TODAY(),"Y")</f>
       </c>
       <c r="J211" s="12"/>
       <c r="K211" s="13"/>
@@ -14925,7 +14904,7 @@
         <v>42708</v>
       </c>
       <c r="I212" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H212,TODAY(),"Y")</f>
       </c>
       <c r="J212" s="12"/>
       <c r="K212" s="13"/>
@@ -14961,7 +14940,7 @@
         <v>36975</v>
       </c>
       <c r="I213" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H213,TODAY(),"Y")</f>
       </c>
       <c r="J213" s="12"/>
       <c r="K213" s="13"/>
@@ -14997,7 +14976,7 @@
         <v>34280</v>
       </c>
       <c r="I214" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H214,TODAY(),"Y")</f>
       </c>
       <c r="J214" s="12">
         <v>1</v>
@@ -15039,7 +15018,7 @@
         <v>31248</v>
       </c>
       <c r="I215" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H215,TODAY(),"Y")</f>
       </c>
       <c r="J215" s="12"/>
       <c r="K215" s="13"/>
@@ -15075,7 +15054,7 @@
         <v>39319</v>
       </c>
       <c r="I216" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H216,TODAY(),"Y")</f>
       </c>
       <c r="J216" s="14"/>
       <c r="K216" s="11"/>
@@ -15111,7 +15090,7 @@
         <v>39859</v>
       </c>
       <c r="I217" s="10">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H217,TODAY(),"Y")</f>
       </c>
       <c r="J217" s="12"/>
       <c r="K217" s="13"/>
@@ -15147,7 +15126,7 @@
         <v>41748</v>
       </c>
       <c r="I218" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H218,TODAY(),"Y")</f>
       </c>
       <c r="J218" s="12"/>
       <c r="K218" s="13"/>
@@ -15183,7 +15162,7 @@
         <v>43068</v>
       </c>
       <c r="I219" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H219,TODAY(),"Y")</f>
       </c>
       <c r="J219" s="12"/>
       <c r="K219" s="13"/>
@@ -15219,7 +15198,7 @@
         <v>30322</v>
       </c>
       <c r="I220" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H220,TODAY(),"Y")</f>
       </c>
       <c r="J220" s="12">
         <v>1</v>
@@ -15261,7 +15240,7 @@
         <v>33728</v>
       </c>
       <c r="I221" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H221,TODAY(),"Y")</f>
       </c>
       <c r="J221" s="12"/>
       <c r="K221" s="13"/>
@@ -15297,7 +15276,7 @@
         <v>39160</v>
       </c>
       <c r="I222" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H222,TODAY(),"Y")</f>
       </c>
       <c r="J222" s="12"/>
       <c r="K222" s="13"/>
@@ -15333,7 +15312,7 @@
         <v>41365</v>
       </c>
       <c r="I223" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H223,TODAY(),"Y")</f>
       </c>
       <c r="J223" s="12"/>
       <c r="K223" s="13"/>
@@ -15369,7 +15348,7 @@
         <v>42807</v>
       </c>
       <c r="I224" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H224,TODAY(),"Y")</f>
       </c>
       <c r="J224" s="12"/>
       <c r="K224" s="13"/>
@@ -15405,7 +15384,7 @@
         <v>43571</v>
       </c>
       <c r="I225" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H225,TODAY(),"Y")</f>
       </c>
       <c r="J225" s="14"/>
       <c r="K225" s="11"/>
@@ -15441,7 +15420,7 @@
         <v>41093</v>
       </c>
       <c r="I226" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H226,TODAY(),"Y")</f>
       </c>
       <c r="J226" s="12"/>
       <c r="K226" s="13"/>
@@ -15477,7 +15456,7 @@
         <v>45154</v>
       </c>
       <c r="I227" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H227,TODAY(),"Y")</f>
       </c>
       <c r="J227" s="12"/>
       <c r="K227" s="13"/>
@@ -15513,7 +15492,7 @@
         <v>45154</v>
       </c>
       <c r="I228" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H228,TODAY(),"Y")</f>
       </c>
       <c r="J228" s="12"/>
       <c r="K228" s="13"/>
@@ -15549,7 +15528,7 @@
         <v>32768</v>
       </c>
       <c r="I229" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H229,TODAY(),"Y")</f>
       </c>
       <c r="J229" s="14">
         <v>1</v>
@@ -15591,7 +15570,7 @@
         <v>41770</v>
       </c>
       <c r="I230" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H230,TODAY(),"Y")</f>
       </c>
       <c r="J230" s="12"/>
       <c r="K230" s="13"/>
@@ -15627,7 +15606,7 @@
         <v>34735</v>
       </c>
       <c r="I231" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H231,TODAY(),"Y")</f>
       </c>
       <c r="J231" s="12"/>
       <c r="K231" s="13"/>
@@ -15663,7 +15642,7 @@
         <v>45148</v>
       </c>
       <c r="I232" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H232,TODAY(),"Y")</f>
       </c>
       <c r="J232" s="12"/>
       <c r="K232" s="13"/>
@@ -15699,7 +15678,7 @@
         <v>31885</v>
       </c>
       <c r="I233" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H233,TODAY(),"Y")</f>
       </c>
       <c r="J233" s="14">
         <v>1</v>
@@ -15741,7 +15720,7 @@
         <v>34393</v>
       </c>
       <c r="I234" s="10">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H234,TODAY(),"Y")</f>
       </c>
       <c r="J234" s="12"/>
       <c r="K234" s="13"/>
@@ -15777,7 +15756,7 @@
         <v>44361</v>
       </c>
       <c r="I235" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H235,TODAY(),"Y")</f>
       </c>
       <c r="J235" s="12"/>
       <c r="K235" s="13"/>
@@ -15813,7 +15792,7 @@
         <v>44992</v>
       </c>
       <c r="I236" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H236,TODAY(),"Y")</f>
       </c>
       <c r="J236" s="12"/>
       <c r="K236" s="13"/>
@@ -15849,7 +15828,7 @@
         <v>32509</v>
       </c>
       <c r="I237" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H237,TODAY(),"Y")</f>
       </c>
       <c r="J237" s="12">
         <v>1</v>
@@ -15891,7 +15870,7 @@
         <v>32818</v>
       </c>
       <c r="I238" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H238,TODAY(),"Y")</f>
       </c>
       <c r="J238" s="12"/>
       <c r="K238" s="13"/>
@@ -15927,7 +15906,7 @@
         <v>38696</v>
       </c>
       <c r="I239" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H239,TODAY(),"Y")</f>
       </c>
       <c r="J239" s="12"/>
       <c r="K239" s="13"/>
@@ -15963,7 +15942,7 @@
         <v>40700</v>
       </c>
       <c r="I240" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H240,TODAY(),"Y")</f>
       </c>
       <c r="J240" s="12"/>
       <c r="K240" s="13"/>
@@ -15999,7 +15978,7 @@
         <v>41225</v>
       </c>
       <c r="I241" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H241,TODAY(),"Y")</f>
       </c>
       <c r="J241" s="12"/>
       <c r="K241" s="13"/>
@@ -16035,7 +16014,7 @@
         <v>42035</v>
       </c>
       <c r="I242" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H242,TODAY(),"Y")</f>
       </c>
       <c r="J242" s="12"/>
       <c r="K242" s="13"/>
@@ -16071,7 +16050,7 @@
         <v>37736</v>
       </c>
       <c r="I243" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H243,TODAY(),"Y")</f>
       </c>
       <c r="J243" s="14"/>
       <c r="K243" s="11"/>
@@ -16107,7 +16086,7 @@
         <v>44445</v>
       </c>
       <c r="I244" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H244,TODAY(),"Y")</f>
       </c>
       <c r="J244" s="12"/>
       <c r="K244" s="13"/>
@@ -16143,7 +16122,7 @@
         <v>44638</v>
       </c>
       <c r="I245" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H245,TODAY(),"Y")</f>
       </c>
       <c r="J245" s="12"/>
       <c r="K245" s="13"/>
@@ -16179,7 +16158,7 @@
         <v>29048</v>
       </c>
       <c r="I246" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H246,TODAY(),"Y")</f>
       </c>
       <c r="J246" s="12">
         <v>0</v>
@@ -16221,7 +16200,7 @@
         <v>27164</v>
       </c>
       <c r="I247" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H247,TODAY(),"Y")</f>
       </c>
       <c r="J247" s="12">
         <v>1</v>
@@ -16263,7 +16242,7 @@
         <v>31457</v>
       </c>
       <c r="I248" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H248,TODAY(),"Y")</f>
       </c>
       <c r="J248" s="12"/>
       <c r="K248" s="13"/>
@@ -16299,7 +16278,7 @@
         <v>41182</v>
       </c>
       <c r="I249" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H249,TODAY(),"Y")</f>
       </c>
       <c r="J249" s="12"/>
       <c r="K249" s="13"/>
@@ -16335,7 +16314,7 @@
         <v>42664</v>
       </c>
       <c r="I250" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H250,TODAY(),"Y")</f>
       </c>
       <c r="J250" s="12"/>
       <c r="K250" s="13"/>
@@ -16371,7 +16350,7 @@
         <v>26131</v>
       </c>
       <c r="I251" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H251,TODAY(),"Y")</f>
       </c>
       <c r="J251" s="12">
         <v>1</v>
@@ -16413,7 +16392,7 @@
         <v>30803</v>
       </c>
       <c r="I252" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H252,TODAY(),"Y")</f>
       </c>
       <c r="J252" s="12"/>
       <c r="K252" s="13"/>
@@ -16449,7 +16428,7 @@
         <v>38083</v>
       </c>
       <c r="I253" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H253,TODAY(),"Y")</f>
       </c>
       <c r="J253" s="12"/>
       <c r="K253" s="13"/>
@@ -16485,7 +16464,7 @@
         <v>40577</v>
       </c>
       <c r="I254" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H254,TODAY(),"Y")</f>
       </c>
       <c r="J254" s="14"/>
       <c r="K254" s="11"/>
@@ -16521,7 +16500,7 @@
         <v>41576</v>
       </c>
       <c r="I255" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H255,TODAY(),"Y")</f>
       </c>
       <c r="J255" s="12"/>
       <c r="K255" s="13"/>
@@ -16557,7 +16536,7 @@
         <v>42519</v>
       </c>
       <c r="I256" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H256,TODAY(),"Y")</f>
       </c>
       <c r="J256" s="12"/>
       <c r="K256" s="13"/>
@@ -16593,7 +16572,7 @@
         <v>36694</v>
       </c>
       <c r="I257" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H257,TODAY(),"Y")</f>
       </c>
       <c r="J257" s="14"/>
       <c r="K257" s="11"/>
@@ -16629,7 +16608,7 @@
         <v>46159</v>
       </c>
       <c r="I258" s="9">
-        <f ca="1" t="shared" si="3"/>
+        <f>DATEDIF(H258,TODAY(),"Y")</f>
       </c>
       <c r="J258" s="12"/>
       <c r="K258" s="13"/>
@@ -16667,7 +16646,7 @@
         <v>33329</v>
       </c>
       <c r="I259" s="9">
-        <f ca="1" t="shared" ref="I259:I322" si="4">DATEDIF(H259,TODAY(),"Y")</f>
+        <f>DATEDIF(H259,TODAY(),"Y")</f>
       </c>
       <c r="J259" s="12">
         <v>1</v>
@@ -16709,7 +16688,7 @@
         <v>34877</v>
       </c>
       <c r="I260" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H260,TODAY(),"Y")</f>
       </c>
       <c r="J260" s="14"/>
       <c r="K260" s="11"/>
@@ -16745,7 +16724,7 @@
         <v>45442</v>
       </c>
       <c r="I261" s="10">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H261,TODAY(),"Y")</f>
       </c>
       <c r="J261" s="12"/>
       <c r="K261" s="13"/>
@@ -16781,7 +16760,7 @@
         <v>24105</v>
       </c>
       <c r="I262" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H262,TODAY(),"Y")</f>
       </c>
       <c r="J262" s="12">
         <v>1</v>
@@ -16823,7 +16802,7 @@
         <v>32014</v>
       </c>
       <c r="I263" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H263,TODAY(),"Y")</f>
       </c>
       <c r="J263" s="12"/>
       <c r="K263" s="13"/>
@@ -16859,7 +16838,7 @@
         <v>45517</v>
       </c>
       <c r="I264" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H264,TODAY(),"Y")</f>
       </c>
       <c r="J264" s="14"/>
       <c r="K264" s="11"/>
@@ -16895,7 +16874,7 @@
         <v>46161</v>
       </c>
       <c r="I265" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H265,TODAY(),"Y")</f>
       </c>
       <c r="J265" s="12"/>
       <c r="K265" s="13"/>
@@ -16933,7 +16912,7 @@
         <v>28924</v>
       </c>
       <c r="I266" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H266,TODAY(),"Y")</f>
       </c>
       <c r="J266" s="12">
         <v>1</v>
@@ -16975,7 +16954,7 @@
         <v>32762</v>
       </c>
       <c r="I267" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H267,TODAY(),"Y")</f>
       </c>
       <c r="J267" s="12"/>
       <c r="K267" s="13"/>
@@ -17011,7 +16990,7 @@
         <v>44210</v>
       </c>
       <c r="I268" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H268,TODAY(),"Y")</f>
       </c>
       <c r="J268" s="12"/>
       <c r="K268" s="13"/>
@@ -17047,7 +17026,7 @@
         <v>44932</v>
       </c>
       <c r="I269" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H269,TODAY(),"Y")</f>
       </c>
       <c r="J269" s="12"/>
       <c r="K269" s="13"/>
@@ -17083,7 +17062,7 @@
         <v>28866</v>
       </c>
       <c r="I270" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H270,TODAY(),"Y")</f>
       </c>
       <c r="J270" s="12">
         <v>1</v>
@@ -17125,7 +17104,7 @@
         <v>29451</v>
       </c>
       <c r="I271" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H271,TODAY(),"Y")</f>
       </c>
       <c r="J271" s="14"/>
       <c r="K271" s="11"/>
@@ -17161,7 +17140,7 @@
         <v>39605</v>
       </c>
       <c r="I272" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H272,TODAY(),"Y")</f>
       </c>
       <c r="J272" s="12"/>
       <c r="K272" s="13"/>
@@ -17197,7 +17176,7 @@
         <v>40310</v>
       </c>
       <c r="I273" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H273,TODAY(),"Y")</f>
       </c>
       <c r="J273" s="12"/>
       <c r="K273" s="13"/>
@@ -17233,7 +17212,7 @@
         <v>41975</v>
       </c>
       <c r="I274" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H274,TODAY(),"Y")</f>
       </c>
       <c r="J274" s="12"/>
       <c r="K274" s="13"/>
@@ -17269,7 +17248,7 @@
         <v>42459</v>
       </c>
       <c r="I275" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H275,TODAY(),"Y")</f>
       </c>
       <c r="J275" s="12"/>
       <c r="K275" s="11"/>
@@ -17305,7 +17284,7 @@
         <v>45660</v>
       </c>
       <c r="I276" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H276,TODAY(),"Y")</f>
       </c>
       <c r="J276" s="12"/>
       <c r="K276" s="13"/>
@@ -17341,7 +17320,7 @@
         <v>31273</v>
       </c>
       <c r="I277" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H277,TODAY(),"Y")</f>
       </c>
       <c r="J277" s="12">
         <v>1</v>
@@ -17383,7 +17362,7 @@
         <v>41542</v>
       </c>
       <c r="I278" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H278,TODAY(),"Y")</f>
       </c>
       <c r="J278" s="14"/>
       <c r="K278" s="11"/>
@@ -17419,7 +17398,7 @@
         <v>36025</v>
       </c>
       <c r="I279" s="10">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H279,TODAY(),"Y")</f>
       </c>
       <c r="J279" s="12"/>
       <c r="K279" s="13"/>
@@ -17455,7 +17434,7 @@
         <v>45418</v>
       </c>
       <c r="I280" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H280,TODAY(),"Y")</f>
       </c>
       <c r="J280" s="12"/>
       <c r="K280" s="13"/>
@@ -17491,7 +17470,7 @@
         <v>29730</v>
       </c>
       <c r="I281" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H281,TODAY(),"Y")</f>
       </c>
       <c r="J281" s="12">
         <v>0</v>
@@ -17533,7 +17512,7 @@
         <v>40800</v>
       </c>
       <c r="I282" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H282,TODAY(),"Y")</f>
       </c>
       <c r="J282" s="12"/>
       <c r="K282" s="13"/>
@@ -17569,7 +17548,7 @@
         <v>41702</v>
       </c>
       <c r="I283" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H283,TODAY(),"Y")</f>
       </c>
       <c r="J283" s="12"/>
       <c r="K283" s="13"/>
@@ -17605,7 +17584,7 @@
         <v>30405</v>
       </c>
       <c r="I284" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H284,TODAY(),"Y")</f>
       </c>
       <c r="J284" s="12">
         <v>1</v>
@@ -17647,7 +17626,7 @@
         <v>33065</v>
       </c>
       <c r="I285" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H285,TODAY(),"Y")</f>
       </c>
       <c r="J285" s="14"/>
       <c r="K285" s="11"/>
@@ -17683,7 +17662,7 @@
         <v>40462</v>
       </c>
       <c r="I286" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H286,TODAY(),"Y")</f>
       </c>
       <c r="J286" s="12"/>
       <c r="K286" s="13"/>
@@ -17721,7 +17700,7 @@
         <v>43990</v>
       </c>
       <c r="I287" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H287,TODAY(),"Y")</f>
       </c>
       <c r="J287" s="12"/>
       <c r="K287" s="13"/>
@@ -17757,7 +17736,7 @@
         <v>42390</v>
       </c>
       <c r="I288" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H288,TODAY(),"Y")</f>
       </c>
       <c r="J288" s="12"/>
       <c r="K288" s="13"/>
@@ -17793,7 +17772,7 @@
         <v>44905</v>
       </c>
       <c r="I289" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H289,TODAY(),"Y")</f>
       </c>
       <c r="J289" s="12"/>
       <c r="K289" s="13"/>
@@ -17829,7 +17808,7 @@
         <v>46061</v>
       </c>
       <c r="I290" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H290,TODAY(),"Y")</f>
       </c>
       <c r="J290" s="14"/>
       <c r="K290" s="11"/>
@@ -17865,7 +17844,7 @@
         <v>32519</v>
       </c>
       <c r="I291" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H291,TODAY(),"Y")</f>
       </c>
       <c r="J291" s="12">
         <v>1</v>
@@ -17907,7 +17886,7 @@
         <v>34772</v>
       </c>
       <c r="I292" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H292,TODAY(),"Y")</f>
       </c>
       <c r="J292" s="12"/>
       <c r="K292" s="13"/>
@@ -17943,7 +17922,7 @@
         <v>44163</v>
       </c>
       <c r="I293" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H293,TODAY(),"Y")</f>
       </c>
       <c r="J293" s="12"/>
       <c r="K293" s="13"/>
@@ -17979,7 +17958,7 @@
         <v>44710</v>
       </c>
       <c r="I294" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H294,TODAY(),"Y")</f>
       </c>
       <c r="J294" s="12"/>
       <c r="K294" s="13"/>
@@ -18015,7 +17994,7 @@
         <v>42965</v>
       </c>
       <c r="I295" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H295,TODAY(),"Y")</f>
       </c>
       <c r="J295" s="14"/>
       <c r="K295" s="11"/>
@@ -18051,7 +18030,7 @@
         <v>27867</v>
       </c>
       <c r="I296" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H296,TODAY(),"Y")</f>
       </c>
       <c r="J296" s="12">
         <v>1</v>
@@ -18093,7 +18072,7 @@
         <v>27413</v>
       </c>
       <c r="I297" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H297,TODAY(),"Y")</f>
       </c>
       <c r="J297" s="12"/>
       <c r="K297" s="13"/>
@@ -18129,7 +18108,7 @@
         <v>44124</v>
       </c>
       <c r="I298" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H298,TODAY(),"Y")</f>
       </c>
       <c r="J298" s="12"/>
       <c r="K298" s="13"/>
@@ -18165,7 +18144,7 @@
         <v>41044</v>
       </c>
       <c r="I299" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H299,TODAY(),"Y")</f>
       </c>
       <c r="J299" s="14"/>
       <c r="K299" s="11"/>
@@ -18201,7 +18180,7 @@
         <v>39426</v>
       </c>
       <c r="I300" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H300,TODAY(),"Y")</f>
       </c>
       <c r="J300" s="12"/>
       <c r="K300" s="13"/>
@@ -18237,7 +18216,7 @@
         <v>31590</v>
       </c>
       <c r="I301" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H301,TODAY(),"Y")</f>
       </c>
       <c r="J301" s="12">
         <v>1</v>
@@ -18279,7 +18258,7 @@
         <v>35322</v>
       </c>
       <c r="I302" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H302,TODAY(),"Y")</f>
       </c>
       <c r="J302" s="12"/>
       <c r="K302" s="13"/>
@@ -18315,7 +18294,7 @@
         <v>44466</v>
       </c>
       <c r="I303" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H303,TODAY(),"Y")</f>
       </c>
       <c r="J303" s="12"/>
       <c r="K303" s="13"/>
@@ -18351,7 +18330,7 @@
         <v>45121</v>
       </c>
       <c r="I304" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H304,TODAY(),"Y")</f>
       </c>
       <c r="J304" s="12"/>
       <c r="K304" s="13"/>
@@ -18387,7 +18366,7 @@
         <v>25543</v>
       </c>
       <c r="I305" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H305,TODAY(),"Y")</f>
       </c>
       <c r="J305" s="12">
         <v>1</v>
@@ -18429,7 +18408,7 @@
         <v>26833</v>
       </c>
       <c r="I306" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H306,TODAY(),"Y")</f>
       </c>
       <c r="J306" s="14"/>
       <c r="K306" s="11"/>
@@ -18465,7 +18444,7 @@
         <v>38511</v>
       </c>
       <c r="I307" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H307,TODAY(),"Y")</f>
       </c>
       <c r="J307" s="12"/>
       <c r="K307" s="13"/>
@@ -18501,7 +18480,7 @@
         <v>39160</v>
       </c>
       <c r="I308" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H308,TODAY(),"Y")</f>
       </c>
       <c r="J308" s="12"/>
       <c r="K308" s="13"/>
@@ -18537,7 +18516,7 @@
         <v>42194</v>
       </c>
       <c r="I309" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H309,TODAY(),"Y")</f>
       </c>
       <c r="J309" s="12"/>
       <c r="K309" s="13"/>
@@ -18573,7 +18552,7 @@
         <v>37602</v>
       </c>
       <c r="I310" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H310,TODAY(),"Y")</f>
       </c>
       <c r="J310" s="12"/>
       <c r="K310" s="13"/>
@@ -18609,7 +18588,7 @@
         <v>44118</v>
       </c>
       <c r="I311" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H311,TODAY(),"Y")</f>
       </c>
       <c r="J311" s="14"/>
       <c r="K311" s="11"/>
@@ -18645,7 +18624,7 @@
         <v>31575</v>
       </c>
       <c r="I312" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H312,TODAY(),"Y")</f>
       </c>
       <c r="J312" s="12">
         <v>1</v>
@@ -18687,7 +18666,7 @@
         <v>31920</v>
       </c>
       <c r="I313" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H313,TODAY(),"Y")</f>
       </c>
       <c r="J313" s="12"/>
       <c r="K313" s="13"/>
@@ -18723,7 +18702,7 @@
         <v>43502</v>
       </c>
       <c r="I314" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H314,TODAY(),"Y")</f>
       </c>
       <c r="J314" s="12"/>
       <c r="K314" s="13"/>
@@ -18759,7 +18738,7 @@
         <v>44313</v>
       </c>
       <c r="I315" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H315,TODAY(),"Y")</f>
       </c>
       <c r="J315" s="12"/>
       <c r="K315" s="13"/>
@@ -18795,7 +18774,7 @@
         <v>45463</v>
       </c>
       <c r="I316" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H316,TODAY(),"Y")</f>
       </c>
       <c r="J316" s="12"/>
       <c r="K316" s="13"/>
@@ -18831,7 +18810,7 @@
         <v>33072</v>
       </c>
       <c r="I317" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H317,TODAY(),"Y")</f>
       </c>
       <c r="J317" s="12">
         <v>1</v>
@@ -18873,7 +18852,7 @@
         <v>33565</v>
       </c>
       <c r="I318" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H318,TODAY(),"Y")</f>
       </c>
       <c r="J318" s="14"/>
       <c r="K318" s="15"/>
@@ -18909,7 +18888,7 @@
         <v>43151</v>
       </c>
       <c r="I319" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H319,TODAY(),"Y")</f>
       </c>
       <c r="J319" s="12"/>
       <c r="K319" s="13"/>
@@ -18945,7 +18924,7 @@
         <v>43151</v>
       </c>
       <c r="I320" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H320,TODAY(),"Y")</f>
       </c>
       <c r="J320" s="14"/>
       <c r="K320" s="11"/>
@@ -18981,7 +18960,7 @@
         <v>43692</v>
       </c>
       <c r="I321" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H321,TODAY(),"Y")</f>
       </c>
       <c r="J321" s="12"/>
       <c r="K321" s="13"/>
@@ -19017,7 +18996,7 @@
         <v>44385</v>
       </c>
       <c r="I322" s="9">
-        <f ca="1" t="shared" si="4"/>
+        <f>DATEDIF(H322,TODAY(),"Y")</f>
       </c>
       <c r="J322" s="12"/>
       <c r="K322" s="13"/>
@@ -19053,7 +19032,7 @@
         <v>45564</v>
       </c>
       <c r="I323" s="9">
-        <f ca="1" t="shared" ref="I323:I386" si="5">DATEDIF(H323,TODAY(),"Y")</f>
+        <f>DATEDIF(H323,TODAY(),"Y")</f>
       </c>
       <c r="J323" s="14"/>
       <c r="K323" s="11"/>
@@ -19089,7 +19068,7 @@
         <v>31626</v>
       </c>
       <c r="I324" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H324,TODAY(),"Y")</f>
       </c>
       <c r="J324" s="12">
         <v>1</v>
@@ -19131,7 +19110,7 @@
         <v>34986</v>
       </c>
       <c r="I325" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H325,TODAY(),"Y")</f>
       </c>
       <c r="J325" s="12"/>
       <c r="K325" s="13"/>
@@ -19167,7 +19146,7 @@
         <v>33425</v>
       </c>
       <c r="I326" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H326,TODAY(),"Y")</f>
       </c>
       <c r="J326" s="14">
         <v>1</v>
@@ -19209,7 +19188,7 @@
         <v>37571</v>
       </c>
       <c r="I327" s="10">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H327,TODAY(),"Y")</f>
       </c>
       <c r="J327" s="12"/>
       <c r="K327" s="13"/>
@@ -19245,7 +19224,7 @@
         <v>44735</v>
       </c>
       <c r="I328" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H328,TODAY(),"Y")</f>
       </c>
       <c r="J328" s="12"/>
       <c r="K328" s="13"/>
@@ -19281,7 +19260,7 @@
         <v>28290</v>
       </c>
       <c r="I329" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H329,TODAY(),"Y")</f>
       </c>
       <c r="J329" s="12">
         <v>1</v>
@@ -19323,7 +19302,7 @@
         <v>30011</v>
       </c>
       <c r="I330" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H330,TODAY(),"Y")</f>
       </c>
       <c r="J330" s="12"/>
       <c r="K330" s="13"/>
@@ -19359,7 +19338,7 @@
         <v>44157</v>
       </c>
       <c r="I331" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H331,TODAY(),"Y")</f>
       </c>
       <c r="J331" s="12"/>
       <c r="K331" s="13"/>
@@ -19395,7 +19374,7 @@
         <v>28524</v>
       </c>
       <c r="I332" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H332,TODAY(),"Y")</f>
       </c>
       <c r="J332" s="14">
         <v>1</v>
@@ -19437,7 +19416,7 @@
         <v>30063</v>
       </c>
       <c r="I333" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H333,TODAY(),"Y")</f>
       </c>
       <c r="J333" s="12"/>
       <c r="K333" s="13"/>
@@ -19473,7 +19452,7 @@
         <v>39721</v>
       </c>
       <c r="I334" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H334,TODAY(),"Y")</f>
       </c>
       <c r="J334" s="12"/>
       <c r="K334" s="13"/>
@@ -19509,7 +19488,7 @@
         <v>40538</v>
       </c>
       <c r="I335" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H335,TODAY(),"Y")</f>
       </c>
       <c r="J335" s="12"/>
       <c r="K335" s="13"/>
@@ -19545,7 +19524,7 @@
         <v>41671</v>
       </c>
       <c r="I336" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H336,TODAY(),"Y")</f>
       </c>
       <c r="J336" s="12"/>
       <c r="K336" s="13"/>
@@ -19581,7 +19560,7 @@
         <v>42876</v>
       </c>
       <c r="I337" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H337,TODAY(),"Y")</f>
       </c>
       <c r="J337" s="14"/>
       <c r="K337" s="11"/>
@@ -19617,7 +19596,7 @@
         <v>30284</v>
       </c>
       <c r="I338" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H338,TODAY(),"Y")</f>
       </c>
       <c r="J338" s="12">
         <v>1</v>
@@ -19659,7 +19638,7 @@
         <v>40391</v>
       </c>
       <c r="I339" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H339,TODAY(),"Y")</f>
       </c>
       <c r="J339" s="12"/>
       <c r="K339" s="13"/>
@@ -19695,7 +19674,7 @@
         <v>44960</v>
       </c>
       <c r="I340" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H340,TODAY(),"Y")</f>
       </c>
       <c r="J340" s="12"/>
       <c r="K340" s="13"/>
@@ -19731,7 +19710,7 @@
         <v>35535</v>
       </c>
       <c r="I341" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H341,TODAY(),"Y")</f>
       </c>
       <c r="J341" s="14"/>
       <c r="K341" s="11"/>
@@ -19767,7 +19746,7 @@
         <v>45622</v>
       </c>
       <c r="I342" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H342,TODAY(),"Y")</f>
       </c>
       <c r="J342" s="12"/>
       <c r="K342" s="13"/>
@@ -19803,7 +19782,7 @@
         <v>32730</v>
       </c>
       <c r="I343" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H343,TODAY(),"Y")</f>
       </c>
       <c r="J343" s="12">
         <v>1</v>
@@ -19845,7 +19824,7 @@
         <v>36694</v>
       </c>
       <c r="I344" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H344,TODAY(),"Y")</f>
       </c>
       <c r="J344" s="12"/>
       <c r="K344" s="13"/>
@@ -19881,7 +19860,7 @@
         <v>45224</v>
       </c>
       <c r="I345" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H345,TODAY(),"Y")</f>
       </c>
       <c r="J345" s="12"/>
       <c r="K345" s="13"/>
@@ -19917,7 +19896,7 @@
         <v>45762</v>
       </c>
       <c r="I346" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H346,TODAY(),"Y")</f>
       </c>
       <c r="J346" s="12"/>
       <c r="K346" s="13"/>
@@ -19953,7 +19932,7 @@
         <v>29323</v>
       </c>
       <c r="I347" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H347,TODAY(),"Y")</f>
       </c>
       <c r="J347" s="12">
         <v>1</v>
@@ -19995,7 +19974,7 @@
         <v>31691</v>
       </c>
       <c r="I348" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H348,TODAY(),"Y")</f>
       </c>
       <c r="J348" s="14"/>
       <c r="K348" s="11"/>
@@ -20031,7 +20010,7 @@
         <v>40892</v>
       </c>
       <c r="I349" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H349,TODAY(),"Y")</f>
       </c>
       <c r="J349" s="12"/>
       <c r="K349" s="13"/>
@@ -20067,7 +20046,7 @@
         <v>40892</v>
       </c>
       <c r="I350" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H350,TODAY(),"Y")</f>
       </c>
       <c r="J350" s="12"/>
       <c r="K350" s="13"/>
@@ -20103,7 +20082,7 @@
         <v>42586</v>
       </c>
       <c r="I351" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H351,TODAY(),"Y")</f>
       </c>
       <c r="J351" s="12"/>
       <c r="K351" s="13"/>
@@ -20139,7 +20118,7 @@
         <v>44071</v>
       </c>
       <c r="I352" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H352,TODAY(),"Y")</f>
       </c>
       <c r="J352" s="12"/>
       <c r="K352" s="13"/>
@@ -20175,7 +20154,7 @@
         <v>44071</v>
       </c>
       <c r="I353" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H353,TODAY(),"Y")</f>
       </c>
       <c r="J353" s="12"/>
       <c r="K353" s="13"/>
@@ -20211,7 +20190,7 @@
         <v>30898</v>
       </c>
       <c r="I354" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H354,TODAY(),"Y")</f>
       </c>
       <c r="J354" s="14">
         <v>1</v>
@@ -20253,7 +20232,7 @@
         <v>33408</v>
       </c>
       <c r="I355" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H355,TODAY(),"Y")</f>
       </c>
       <c r="J355" s="12"/>
       <c r="K355" s="13"/>
@@ -20289,7 +20268,7 @@
         <v>41752</v>
       </c>
       <c r="I356" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H356,TODAY(),"Y")</f>
       </c>
       <c r="J356" s="12"/>
       <c r="K356" s="13"/>
@@ -20325,7 +20304,7 @@
         <v>42450</v>
       </c>
       <c r="I357" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H357,TODAY(),"Y")</f>
       </c>
       <c r="J357" s="12"/>
       <c r="K357" s="13"/>
@@ -20361,7 +20340,7 @@
         <v>42873</v>
       </c>
       <c r="I358" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H358,TODAY(),"Y")</f>
       </c>
       <c r="J358" s="12"/>
       <c r="K358" s="13"/>
@@ -20397,7 +20376,7 @@
         <v>44157</v>
       </c>
       <c r="I359" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H359,TODAY(),"Y")</f>
       </c>
       <c r="J359" s="12"/>
       <c r="K359" s="13"/>
@@ -20433,7 +20412,7 @@
         <v>31762</v>
       </c>
       <c r="I360" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H360,TODAY(),"Y")</f>
       </c>
       <c r="J360" s="14">
         <v>1</v>
@@ -20475,7 +20454,7 @@
         <v>35543</v>
       </c>
       <c r="I361" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H361,TODAY(),"Y")</f>
       </c>
       <c r="J361" s="12"/>
       <c r="K361" s="13"/>
@@ -20511,7 +20490,7 @@
         <v>43772</v>
       </c>
       <c r="I362" s="5">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H362,TODAY(),"Y")</f>
       </c>
       <c r="J362" s="12"/>
       <c r="K362" s="13"/>
@@ -20547,7 +20526,7 @@
         <v>44566</v>
       </c>
       <c r="I363" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H363,TODAY(),"Y")</f>
       </c>
       <c r="J363" s="12"/>
       <c r="K363" s="13"/>
@@ -20583,7 +20562,7 @@
         <v>45639</v>
       </c>
       <c r="I364" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H364,TODAY(),"Y")</f>
       </c>
       <c r="J364" s="14"/>
       <c r="K364" s="11"/>
@@ -20619,7 +20598,7 @@
         <v>45996</v>
       </c>
       <c r="I365" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H365,TODAY(),"Y")</f>
       </c>
       <c r="J365" s="12"/>
       <c r="K365" s="13"/>
@@ -20655,7 +20634,7 @@
         <v>29186</v>
       </c>
       <c r="I366" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H366,TODAY(),"Y")</f>
       </c>
       <c r="J366" s="12">
         <v>1</v>
@@ -20697,7 +20676,7 @@
         <v>30503</v>
       </c>
       <c r="I367" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H367,TODAY(),"Y")</f>
       </c>
       <c r="J367" s="14"/>
       <c r="K367" s="11"/>
@@ -20733,7 +20712,7 @@
         <v>43890</v>
       </c>
       <c r="I368" s="10">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H368,TODAY(),"Y")</f>
       </c>
       <c r="J368" s="12"/>
       <c r="K368" s="13"/>
@@ -20769,7 +20748,7 @@
         <v>45389</v>
       </c>
       <c r="I369" s="5">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H369,TODAY(),"Y")</f>
       </c>
       <c r="J369" s="12"/>
       <c r="K369" s="13"/>
@@ -20805,7 +20784,7 @@
         <v>29501</v>
       </c>
       <c r="I370" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H370,TODAY(),"Y")</f>
       </c>
       <c r="J370" s="12">
         <v>1</v>
@@ -20847,7 +20826,7 @@
         <v>31675</v>
       </c>
       <c r="I371" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H371,TODAY(),"Y")</f>
       </c>
       <c r="J371" s="12"/>
       <c r="K371" s="11"/>
@@ -20883,7 +20862,7 @@
         <v>44816</v>
       </c>
       <c r="I372" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H372,TODAY(),"Y")</f>
       </c>
       <c r="J372" s="12"/>
       <c r="K372" s="13"/>
@@ -20919,7 +20898,7 @@
         <v>34515</v>
       </c>
       <c r="I373" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H373,TODAY(),"Y")</f>
       </c>
       <c r="J373" s="12">
         <v>1</v>
@@ -20961,7 +20940,7 @@
         <v>35145</v>
       </c>
       <c r="I374" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H374,TODAY(),"Y")</f>
       </c>
       <c r="J374" s="14"/>
       <c r="K374" s="11"/>
@@ -20997,7 +20976,7 @@
         <v>44181</v>
       </c>
       <c r="I375" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H375,TODAY(),"Y")</f>
       </c>
       <c r="J375" s="12"/>
       <c r="K375" s="13"/>
@@ -21033,7 +21012,7 @@
         <v>44681</v>
       </c>
       <c r="I376" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H376,TODAY(),"Y")</f>
       </c>
       <c r="J376" s="12"/>
       <c r="K376" s="13"/>
@@ -21069,7 +21048,7 @@
         <v>46195</v>
       </c>
       <c r="I377" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H377,TODAY(),"Y")</f>
       </c>
       <c r="J377" s="12"/>
       <c r="K377" s="13"/>
@@ -21107,7 +21086,7 @@
         <v>34125</v>
       </c>
       <c r="I378" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H378,TODAY(),"Y")</f>
       </c>
       <c r="J378" s="14">
         <v>0</v>
@@ -21149,7 +21128,7 @@
         <v>43740</v>
       </c>
       <c r="I379" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H379,TODAY(),"Y")</f>
       </c>
       <c r="J379" s="12"/>
       <c r="K379" s="13"/>
@@ -21185,7 +21164,7 @@
         <v>44723</v>
       </c>
       <c r="I380" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H380,TODAY(),"Y")</f>
       </c>
       <c r="J380" s="14"/>
       <c r="K380" s="15"/>
@@ -21221,7 +21200,7 @@
         <v>31105</v>
       </c>
       <c r="I381" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H381,TODAY(),"Y")</f>
       </c>
       <c r="J381" s="12">
         <v>1</v>
@@ -21263,7 +21242,7 @@
         <v>28282</v>
       </c>
       <c r="I382" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H382,TODAY(),"Y")</f>
       </c>
       <c r="J382" s="14"/>
       <c r="K382" s="15"/>
@@ -21299,7 +21278,7 @@
         <v>40585</v>
       </c>
       <c r="I383" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H383,TODAY(),"Y")</f>
       </c>
       <c r="J383" s="12"/>
       <c r="K383" s="13"/>
@@ -21335,7 +21314,7 @@
         <v>41803</v>
       </c>
       <c r="I384" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H384,TODAY(),"Y")</f>
       </c>
       <c r="J384" s="12"/>
       <c r="K384" s="11"/>
@@ -21371,7 +21350,7 @@
         <v>31172</v>
       </c>
       <c r="I385" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H385,TODAY(),"Y")</f>
       </c>
       <c r="J385" s="12">
         <v>1</v>
@@ -21413,7 +21392,7 @@
         <v>33760</v>
       </c>
       <c r="I386" s="9">
-        <f ca="1" t="shared" si="5"/>
+        <f>DATEDIF(H386,TODAY(),"Y")</f>
       </c>
       <c r="J386" s="12"/>
       <c r="K386" s="13"/>
@@ -21449,7 +21428,7 @@
         <v>33232</v>
       </c>
       <c r="I387" s="9">
-        <f ca="1" t="shared" ref="I387:I450" si="6">DATEDIF(H387,TODAY(),"Y")</f>
+        <f>DATEDIF(H387,TODAY(),"Y")</f>
       </c>
       <c r="J387" s="12">
         <v>1</v>
@@ -21491,7 +21470,7 @@
         <v>37086</v>
       </c>
       <c r="I388" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H388,TODAY(),"Y")</f>
       </c>
       <c r="J388" s="12"/>
       <c r="K388" s="13"/>
@@ -21527,7 +21506,7 @@
         <v>32406</v>
       </c>
       <c r="I389" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H389,TODAY(),"Y")</f>
       </c>
       <c r="J389" s="14">
         <v>1</v>
@@ -21569,7 +21548,7 @@
         <v>27282</v>
       </c>
       <c r="I390" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H390,TODAY(),"Y")</f>
       </c>
       <c r="J390" s="12"/>
       <c r="K390" s="13"/>
@@ -21605,7 +21584,7 @@
         <v>32600</v>
       </c>
       <c r="I391" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H391,TODAY(),"Y")</f>
       </c>
       <c r="J391" s="12">
         <v>0</v>
@@ -21647,7 +21626,7 @@
         <v>40523</v>
       </c>
       <c r="I392" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H392,TODAY(),"Y")</f>
       </c>
       <c r="J392" s="14"/>
       <c r="K392" s="11"/>
@@ -21683,7 +21662,7 @@
         <v>44288</v>
       </c>
       <c r="I393" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H393,TODAY(),"Y")</f>
       </c>
       <c r="J393" s="12"/>
       <c r="K393" s="13"/>
@@ -21719,7 +21698,7 @@
         <v>43361</v>
       </c>
       <c r="I394" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H394,TODAY(),"Y")</f>
       </c>
       <c r="J394" s="12"/>
       <c r="K394" s="13"/>
@@ -21755,7 +21734,7 @@
         <v>45115</v>
       </c>
       <c r="I395" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H395,TODAY(),"Y")</f>
       </c>
       <c r="J395" s="12"/>
       <c r="K395" s="13"/>
@@ -21791,7 +21770,7 @@
         <v>32373</v>
       </c>
       <c r="I396" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H396,TODAY(),"Y")</f>
       </c>
       <c r="J396" s="12">
         <v>1</v>
@@ -21833,7 +21812,7 @@
         <v>32453</v>
       </c>
       <c r="I397" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H397,TODAY(),"Y")</f>
       </c>
       <c r="J397" s="12"/>
       <c r="K397" s="13"/>
@@ -21869,7 +21848,7 @@
         <v>44567</v>
       </c>
       <c r="I398" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H398,TODAY(),"Y")</f>
       </c>
       <c r="J398" s="12"/>
       <c r="K398" s="13"/>
@@ -21905,7 +21884,7 @@
         <v>44567</v>
       </c>
       <c r="I399" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H399,TODAY(),"Y")</f>
       </c>
       <c r="J399" s="12"/>
       <c r="K399" s="13"/>
@@ -21943,7 +21922,7 @@
         <v>27307</v>
       </c>
       <c r="I400" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H400,TODAY(),"Y")</f>
       </c>
       <c r="J400" s="12">
         <v>1</v>
@@ -21985,7 +21964,7 @@
         <v>31813</v>
       </c>
       <c r="I401" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H401,TODAY(),"Y")</f>
       </c>
       <c r="J401" s="14"/>
       <c r="K401" s="11"/>
@@ -22021,7 +22000,7 @@
         <v>40519</v>
       </c>
       <c r="I402" s="10">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H402,TODAY(),"Y")</f>
       </c>
       <c r="J402" s="12"/>
       <c r="K402" s="13"/>
@@ -22057,7 +22036,7 @@
         <v>38088</v>
       </c>
       <c r="I403" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H403,TODAY(),"Y")</f>
       </c>
       <c r="J403" s="12"/>
       <c r="K403" s="13"/>
@@ -22093,7 +22072,7 @@
         <v>32060</v>
       </c>
       <c r="I404" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H404,TODAY(),"Y")</f>
       </c>
       <c r="J404" s="12">
         <v>0</v>
@@ -22135,7 +22114,7 @@
         <v>39929</v>
       </c>
       <c r="I405" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H405,TODAY(),"Y")</f>
       </c>
       <c r="J405" s="12"/>
       <c r="K405" s="13"/>
@@ -22171,7 +22150,7 @@
         <v>41411</v>
       </c>
       <c r="I406" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H406,TODAY(),"Y")</f>
       </c>
       <c r="J406" s="12"/>
       <c r="K406" s="13"/>
@@ -22207,7 +22186,7 @@
         <v>43028</v>
       </c>
       <c r="I407" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H407,TODAY(),"Y")</f>
       </c>
       <c r="J407" s="14"/>
       <c r="K407" s="11"/>
@@ -22243,7 +22222,7 @@
         <v>45157</v>
       </c>
       <c r="I408" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H408,TODAY(),"Y")</f>
       </c>
       <c r="J408" s="12"/>
       <c r="K408" s="13"/>
@@ -22279,7 +22258,7 @@
         <v>29763</v>
       </c>
       <c r="I409" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H409,TODAY(),"Y")</f>
       </c>
       <c r="J409" s="12">
         <v>1</v>
@@ -22321,7 +22300,7 @@
         <v>32614</v>
       </c>
       <c r="I410" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H410,TODAY(),"Y")</f>
       </c>
       <c r="J410" s="12"/>
       <c r="K410" s="13"/>
@@ -22357,7 +22336,7 @@
         <v>40567</v>
       </c>
       <c r="I411" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H411,TODAY(),"Y")</f>
       </c>
       <c r="J411" s="12"/>
       <c r="K411" s="13"/>
@@ -22393,7 +22372,7 @@
         <v>41697</v>
       </c>
       <c r="I412" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H412,TODAY(),"Y")</f>
       </c>
       <c r="J412" s="12"/>
       <c r="K412" s="13"/>
@@ -22429,7 +22408,7 @@
         <v>43432</v>
       </c>
       <c r="I413" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H413,TODAY(),"Y")</f>
       </c>
       <c r="J413" s="12"/>
       <c r="K413" s="13"/>
@@ -22465,7 +22444,7 @@
         <v>44940</v>
       </c>
       <c r="I414" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H414,TODAY(),"Y")</f>
       </c>
       <c r="J414" s="14"/>
       <c r="K414" s="11"/>
@@ -22501,7 +22480,7 @@
         <v>30206</v>
       </c>
       <c r="I415" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H415,TODAY(),"Y")</f>
       </c>
       <c r="J415" s="12">
         <v>1</v>
@@ -22543,7 +22522,7 @@
         <v>31156</v>
       </c>
       <c r="I416" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H416,TODAY(),"Y")</f>
       </c>
       <c r="J416" s="12"/>
       <c r="K416" s="13"/>
@@ -22579,7 +22558,7 @@
         <v>38449</v>
       </c>
       <c r="I417" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H417,TODAY(),"Y")</f>
       </c>
       <c r="J417" s="12"/>
       <c r="K417" s="13"/>
@@ -22615,7 +22594,7 @@
         <v>43869</v>
       </c>
       <c r="I418" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H418,TODAY(),"Y")</f>
       </c>
       <c r="J418" s="12"/>
       <c r="K418" s="13"/>
@@ -22651,7 +22630,7 @@
         <v>37025</v>
       </c>
       <c r="I419" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H419,TODAY(),"Y")</f>
       </c>
       <c r="J419" s="14"/>
       <c r="K419" s="11"/>
@@ -22687,7 +22666,7 @@
         <v>44524</v>
       </c>
       <c r="I420" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H420,TODAY(),"Y")</f>
       </c>
       <c r="J420" s="12"/>
       <c r="K420" s="13"/>
@@ -22723,7 +22702,7 @@
         <v>41536</v>
       </c>
       <c r="I421" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H421,TODAY(),"Y")</f>
       </c>
       <c r="J421" s="12"/>
       <c r="K421" s="13"/>
@@ -22759,7 +22738,7 @@
         <v>28560</v>
       </c>
       <c r="I422" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H422,TODAY(),"Y")</f>
       </c>
       <c r="J422" s="12">
         <v>1</v>
@@ -22801,7 +22780,7 @@
         <v>31995</v>
       </c>
       <c r="I423" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H423,TODAY(),"Y")</f>
       </c>
       <c r="J423" s="14"/>
       <c r="K423" s="11"/>
@@ -22837,7 +22816,7 @@
         <v>41371</v>
       </c>
       <c r="I424" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H424,TODAY(),"Y")</f>
       </c>
       <c r="J424" s="12"/>
       <c r="K424" s="13"/>
@@ -22873,7 +22852,7 @@
         <v>41855</v>
       </c>
       <c r="I425" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H425,TODAY(),"Y")</f>
       </c>
       <c r="J425" s="12"/>
       <c r="K425" s="13"/>
@@ -22909,7 +22888,7 @@
         <v>44047</v>
       </c>
       <c r="I426" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H426,TODAY(),"Y")</f>
       </c>
       <c r="J426" s="12"/>
       <c r="K426" s="13"/>
@@ -22945,7 +22924,7 @@
         <v>32347</v>
       </c>
       <c r="I427" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H427,TODAY(),"Y")</f>
       </c>
       <c r="J427" s="12">
         <v>1</v>
@@ -22987,7 +22966,7 @@
         <v>43971</v>
       </c>
       <c r="I428" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H428,TODAY(),"Y")</f>
       </c>
       <c r="J428" s="12"/>
       <c r="K428" s="13"/>
@@ -23023,7 +23002,7 @@
         <v>43033</v>
       </c>
       <c r="I429" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H429,TODAY(),"Y")</f>
       </c>
       <c r="J429" s="12"/>
       <c r="K429" s="13"/>
@@ -23059,7 +23038,7 @@
         <v>43971</v>
       </c>
       <c r="I430" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H430,TODAY(),"Y")</f>
       </c>
       <c r="J430" s="12"/>
       <c r="K430" s="11"/>
@@ -23095,7 +23074,7 @@
         <v>25820</v>
       </c>
       <c r="I431" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H431,TODAY(),"Y")</f>
       </c>
       <c r="J431" s="12">
         <v>1</v>
@@ -23137,7 +23116,7 @@
         <v>37709</v>
       </c>
       <c r="I432" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H432,TODAY(),"Y")</f>
       </c>
       <c r="J432" s="12"/>
       <c r="K432" s="13"/>
@@ -23173,7 +23152,7 @@
         <v>38960</v>
       </c>
       <c r="I433" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H433,TODAY(),"Y")</f>
       </c>
       <c r="J433" s="14"/>
       <c r="K433" s="11"/>
@@ -23209,7 +23188,7 @@
         <v>41858</v>
       </c>
       <c r="I434" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H434,TODAY(),"Y")</f>
       </c>
       <c r="J434" s="12"/>
       <c r="K434" s="13"/>
@@ -23245,7 +23224,7 @@
         <v>36596</v>
       </c>
       <c r="I435" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H435,TODAY(),"Y")</f>
       </c>
       <c r="J435" s="12"/>
       <c r="K435" s="13"/>
@@ -23281,7 +23260,7 @@
         <v>31170</v>
       </c>
       <c r="I436" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H436,TODAY(),"Y")</f>
       </c>
       <c r="J436" s="12"/>
       <c r="K436" s="13"/>
@@ -23317,7 +23296,7 @@
         <v>45875</v>
       </c>
       <c r="I437" s="5">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H437,TODAY(),"Y")</f>
       </c>
       <c r="J437" s="12"/>
       <c r="K437" s="13"/>
@@ -23353,7 +23332,7 @@
         <v>30546</v>
       </c>
       <c r="I438" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H438,TODAY(),"Y")</f>
       </c>
       <c r="J438" s="12">
         <v>0</v>
@@ -23395,7 +23374,7 @@
         <v>39975</v>
       </c>
       <c r="I439" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H439,TODAY(),"Y")</f>
       </c>
       <c r="J439" s="12"/>
       <c r="K439" s="13"/>
@@ -23431,7 +23410,7 @@
         <v>38224</v>
       </c>
       <c r="I440" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H440,TODAY(),"Y")</f>
       </c>
       <c r="J440" s="14"/>
       <c r="K440" s="11"/>
@@ -23467,7 +23446,7 @@
         <v>25800</v>
       </c>
       <c r="I441" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H441,TODAY(),"Y")</f>
       </c>
       <c r="J441" s="12">
         <v>1</v>
@@ -23509,7 +23488,7 @@
         <v>29642</v>
       </c>
       <c r="I442" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H442,TODAY(),"Y")</f>
       </c>
       <c r="J442" s="12"/>
       <c r="K442" s="13"/>
@@ -23545,7 +23524,7 @@
         <v>40510</v>
       </c>
       <c r="I443" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H443,TODAY(),"Y")</f>
       </c>
       <c r="J443" s="12"/>
       <c r="K443" s="13"/>
@@ -23581,7 +23560,7 @@
         <v>41534</v>
       </c>
       <c r="I444" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H444,TODAY(),"Y")</f>
       </c>
       <c r="J444" s="12"/>
       <c r="K444" s="13"/>
@@ -23617,7 +23596,7 @@
         <v>42478</v>
       </c>
       <c r="I445" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H445,TODAY(),"Y")</f>
       </c>
       <c r="J445" s="12"/>
       <c r="K445" s="13"/>
@@ -23653,7 +23632,7 @@
         <v>44112</v>
       </c>
       <c r="I446" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H446,TODAY(),"Y")</f>
       </c>
       <c r="J446" s="14"/>
       <c r="K446" s="11"/>
@@ -23689,7 +23668,7 @@
         <v>40673</v>
       </c>
       <c r="I447" s="10">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H447,TODAY(),"Y")</f>
       </c>
       <c r="J447" s="12"/>
       <c r="K447" s="13"/>
@@ -23725,7 +23704,7 @@
         <v>28210</v>
       </c>
       <c r="I448" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H448,TODAY(),"Y")</f>
       </c>
       <c r="J448" s="12">
         <v>1</v>
@@ -23767,7 +23746,7 @@
         <v>31431</v>
       </c>
       <c r="I449" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H449,TODAY(),"Y")</f>
       </c>
       <c r="J449" s="12"/>
       <c r="K449" s="13"/>
@@ -23803,7 +23782,7 @@
         <v>39483</v>
       </c>
       <c r="I450" s="9">
-        <f ca="1" t="shared" si="6"/>
+        <f>DATEDIF(H450,TODAY(),"Y")</f>
       </c>
       <c r="J450" s="14"/>
       <c r="K450" s="11"/>
@@ -23839,7 +23818,7 @@
         <v>42677</v>
       </c>
       <c r="I451" s="10">
-        <f ca="1" t="shared" ref="I451:I514" si="7">DATEDIF(H451,TODAY(),"Y")</f>
+        <f>DATEDIF(H451,TODAY(),"Y")</f>
       </c>
       <c r="J451" s="12"/>
       <c r="K451" s="13"/>
@@ -23875,7 +23854,7 @@
         <v>43388</v>
       </c>
       <c r="I452" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H452,TODAY(),"Y")</f>
       </c>
       <c r="J452" s="12"/>
       <c r="K452" s="13"/>
@@ -23911,7 +23890,7 @@
         <v>44238</v>
       </c>
       <c r="I453" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H453,TODAY(),"Y")</f>
       </c>
       <c r="J453" s="12"/>
       <c r="K453" s="13"/>
@@ -23947,7 +23926,7 @@
         <v>32748</v>
       </c>
       <c r="I454" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H454,TODAY(),"Y")</f>
       </c>
       <c r="J454" s="12">
         <v>1</v>
@@ -23989,7 +23968,7 @@
         <v>35034</v>
       </c>
       <c r="I455" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H455,TODAY(),"Y")</f>
       </c>
       <c r="J455" s="12"/>
       <c r="K455" s="13"/>
@@ -24025,7 +24004,7 @@
         <v>44442</v>
       </c>
       <c r="I456" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H456,TODAY(),"Y")</f>
       </c>
       <c r="J456" s="12"/>
       <c r="K456" s="13"/>
@@ -24061,7 +24040,7 @@
         <v>45545</v>
       </c>
       <c r="I457" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H457,TODAY(),"Y")</f>
       </c>
       <c r="J457" s="14"/>
       <c r="K457" s="11"/>
@@ -24097,7 +24076,7 @@
         <v>23282</v>
       </c>
       <c r="I458" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H458,TODAY(),"Y")</f>
       </c>
       <c r="J458" s="12">
         <v>1</v>
@@ -24139,7 +24118,7 @@
         <v>25185</v>
       </c>
       <c r="I459" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H459,TODAY(),"Y")</f>
       </c>
       <c r="J459" s="12"/>
       <c r="K459" s="13"/>
@@ -24175,7 +24154,7 @@
         <v>41801</v>
       </c>
       <c r="I460" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H460,TODAY(),"Y")</f>
       </c>
       <c r="J460" s="12"/>
       <c r="K460" s="13"/>
@@ -24211,7 +24190,7 @@
         <v>39622</v>
       </c>
       <c r="I461" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H461,TODAY(),"Y")</f>
       </c>
       <c r="J461" s="12"/>
       <c r="K461" s="13"/>
@@ -24247,7 +24226,7 @@
         <v>36555</v>
       </c>
       <c r="I462" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H462,TODAY(),"Y")</f>
       </c>
       <c r="J462" s="12"/>
       <c r="K462" s="13"/>
@@ -24283,7 +24262,7 @@
         <v>38149</v>
       </c>
       <c r="I463" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H463,TODAY(),"Y")</f>
       </c>
       <c r="J463" s="14"/>
       <c r="K463" s="11"/>
@@ -24319,7 +24298,7 @@
         <v>36555</v>
       </c>
       <c r="I464" s="10">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H464,TODAY(),"Y")</f>
       </c>
       <c r="J464" s="12"/>
       <c r="K464" s="13"/>
@@ -24355,7 +24334,7 @@
         <v>26862</v>
       </c>
       <c r="I465" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H465,TODAY(),"Y")</f>
       </c>
       <c r="J465" s="12">
         <v>1</v>
@@ -24397,7 +24376,7 @@
         <v>30527</v>
       </c>
       <c r="I466" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H466,TODAY(),"Y")</f>
       </c>
       <c r="J466" s="12"/>
       <c r="K466" s="13"/>
@@ -24433,7 +24412,7 @@
         <v>40741</v>
       </c>
       <c r="I467" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H467,TODAY(),"Y")</f>
       </c>
       <c r="J467" s="14"/>
       <c r="K467" s="11"/>
@@ -24469,7 +24448,7 @@
         <v>41337</v>
       </c>
       <c r="I468" s="10">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H468,TODAY(),"Y")</f>
       </c>
       <c r="J468" s="12"/>
       <c r="K468" s="13"/>
@@ -24505,7 +24484,7 @@
         <v>43861</v>
       </c>
       <c r="I469" s="5">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H469,TODAY(),"Y")</f>
       </c>
       <c r="J469" s="12"/>
       <c r="K469" s="13"/>
@@ -24541,7 +24520,7 @@
         <v>43861</v>
       </c>
       <c r="I470" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H470,TODAY(),"Y")</f>
       </c>
       <c r="J470" s="12"/>
       <c r="K470" s="13"/>
@@ -24577,7 +24556,7 @@
         <v>33577</v>
       </c>
       <c r="I471" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H471,TODAY(),"Y")</f>
       </c>
       <c r="J471" s="12">
         <v>1</v>
@@ -24619,7 +24598,7 @@
         <v>33646</v>
       </c>
       <c r="I472" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H472,TODAY(),"Y")</f>
       </c>
       <c r="J472" s="12"/>
       <c r="K472" s="13"/>
@@ -24655,7 +24634,7 @@
         <v>43610</v>
       </c>
       <c r="I473" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H473,TODAY(),"Y")</f>
       </c>
       <c r="J473" s="12"/>
       <c r="K473" s="11"/>
@@ -24691,7 +24670,7 @@
         <v>44589</v>
       </c>
       <c r="I474" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H474,TODAY(),"Y")</f>
       </c>
       <c r="J474" s="12"/>
       <c r="K474" s="13"/>
@@ -24727,7 +24706,7 @@
         <v>28513</v>
       </c>
       <c r="I475" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H475,TODAY(),"Y")</f>
       </c>
       <c r="J475" s="14">
         <v>1</v>
@@ -24769,7 +24748,7 @@
         <v>32426</v>
       </c>
       <c r="I476" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H476,TODAY(),"Y")</f>
       </c>
       <c r="J476" s="12"/>
       <c r="K476" s="13"/>
@@ -24805,7 +24784,7 @@
         <v>40339</v>
       </c>
       <c r="I477" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H477,TODAY(),"Y")</f>
       </c>
       <c r="J477" s="12"/>
       <c r="K477" s="13"/>
@@ -24841,7 +24820,7 @@
         <v>44023</v>
       </c>
       <c r="I478" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H478,TODAY(),"Y")</f>
       </c>
       <c r="J478" s="12"/>
       <c r="K478" s="13"/>
@@ -24877,7 +24856,7 @@
         <v>44286</v>
       </c>
       <c r="I479" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H479,TODAY(),"Y")</f>
       </c>
       <c r="J479" s="14"/>
       <c r="K479" s="11"/>
@@ -24913,7 +24892,7 @@
         <v>45076</v>
       </c>
       <c r="I480" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H480,TODAY(),"Y")</f>
       </c>
       <c r="J480" s="12"/>
       <c r="K480" s="13"/>
@@ -24949,7 +24928,7 @@
         <v>27214</v>
       </c>
       <c r="I481" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H481,TODAY(),"Y")</f>
       </c>
       <c r="J481" s="12">
         <v>0</v>
@@ -24991,7 +24970,7 @@
         <v>45061</v>
       </c>
       <c r="I482" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H482,TODAY(),"Y")</f>
       </c>
       <c r="J482" s="12"/>
       <c r="K482" s="13"/>
@@ -25027,7 +25006,7 @@
         <v>32435</v>
       </c>
       <c r="I483" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H483,TODAY(),"Y")</f>
       </c>
       <c r="J483" s="12">
         <v>1</v>
@@ -25069,7 +25048,7 @@
         <v>34436</v>
       </c>
       <c r="I484" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H484,TODAY(),"Y")</f>
       </c>
       <c r="J484" s="12"/>
       <c r="K484" s="13"/>
@@ -25105,7 +25084,7 @@
         <v>44513</v>
       </c>
       <c r="I485" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H485,TODAY(),"Y")</f>
       </c>
       <c r="J485" s="12"/>
       <c r="K485" s="13"/>
@@ -25141,7 +25120,7 @@
         <v>45265</v>
       </c>
       <c r="I486" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H486,TODAY(),"Y")</f>
       </c>
       <c r="J486" s="14"/>
       <c r="K486" s="11"/>
@@ -25177,7 +25156,7 @@
         <v>31705</v>
       </c>
       <c r="I487" s="6">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H487,TODAY(),"Y")</f>
       </c>
       <c r="J487" s="12">
         <v>1</v>
@@ -25219,7 +25198,7 @@
         <v>32182</v>
       </c>
       <c r="I488" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H488,TODAY(),"Y")</f>
       </c>
       <c r="J488" s="12"/>
       <c r="K488" s="13"/>
@@ -25255,7 +25234,7 @@
         <v>44258</v>
       </c>
       <c r="I489" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H489,TODAY(),"Y")</f>
       </c>
       <c r="J489" s="12"/>
       <c r="K489" s="13"/>
@@ -25291,7 +25270,7 @@
         <v>39915</v>
       </c>
       <c r="I490" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H490,TODAY(),"Y")</f>
       </c>
       <c r="J490" s="12"/>
       <c r="K490" s="13"/>
@@ -25327,7 +25306,7 @@
         <v>41504</v>
       </c>
       <c r="I491" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H491,TODAY(),"Y")</f>
       </c>
       <c r="J491" s="12"/>
       <c r="K491" s="13"/>
@@ -25363,7 +25342,7 @@
         <v>42470</v>
       </c>
       <c r="I492" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H492,TODAY(),"Y")</f>
       </c>
       <c r="J492" s="12"/>
       <c r="K492" s="13"/>
@@ -25399,7 +25378,7 @@
         <v>42656</v>
       </c>
       <c r="I493" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H493,TODAY(),"Y")</f>
       </c>
       <c r="J493" s="14"/>
       <c r="K493" s="11"/>
@@ -25435,7 +25414,7 @@
         <v>33662</v>
       </c>
       <c r="I494" s="5">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H494,TODAY(),"Y")</f>
       </c>
       <c r="J494" s="12">
         <v>1</v>
@@ -25477,7 +25456,7 @@
         <v>33971</v>
       </c>
       <c r="I495" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H495,TODAY(),"Y")</f>
       </c>
       <c r="J495" s="12"/>
       <c r="K495" s="13"/>
@@ -25513,7 +25492,7 @@
         <v>40145</v>
       </c>
       <c r="I496" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H496,TODAY(),"Y")</f>
       </c>
       <c r="J496" s="12"/>
       <c r="K496" s="13"/>
@@ -25549,7 +25528,7 @@
         <v>40676</v>
       </c>
       <c r="I497" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H497,TODAY(),"Y")</f>
       </c>
       <c r="J497" s="14"/>
       <c r="K497" s="11"/>
@@ -25585,7 +25564,7 @@
         <v>44109</v>
       </c>
       <c r="I498" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H498,TODAY(),"Y")</f>
       </c>
       <c r="J498" s="12"/>
       <c r="K498" s="13"/>
@@ -25621,7 +25600,7 @@
         <v>42029</v>
       </c>
       <c r="I499" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H499,TODAY(),"Y")</f>
       </c>
       <c r="J499" s="12"/>
       <c r="K499" s="13"/>
@@ -25657,7 +25636,7 @@
         <v>45260</v>
       </c>
       <c r="I500" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H500,TODAY(),"Y")</f>
       </c>
       <c r="J500" s="12"/>
       <c r="K500" s="13"/>
@@ -25693,7 +25672,7 @@
         <v>33567</v>
       </c>
       <c r="I501" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H501,TODAY(),"Y")</f>
       </c>
       <c r="J501" s="12">
         <v>1</v>
@@ -25735,7 +25714,7 @@
         <v>43482</v>
       </c>
       <c r="I502" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H502,TODAY(),"Y")</f>
       </c>
       <c r="J502" s="14"/>
       <c r="K502" s="11"/>
@@ -25771,7 +25750,7 @@
         <v>36143</v>
       </c>
       <c r="I503" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H503,TODAY(),"Y")</f>
       </c>
       <c r="J503" s="12"/>
       <c r="K503" s="13"/>
@@ -25807,7 +25786,7 @@
         <v>45285</v>
       </c>
       <c r="I504" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H504,TODAY(),"Y")</f>
       </c>
       <c r="J504" s="12"/>
       <c r="K504" s="13"/>
@@ -25843,7 +25822,7 @@
         <v>32408</v>
       </c>
       <c r="I505" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H505,TODAY(),"Y")</f>
       </c>
       <c r="J505" s="12">
         <v>1</v>
@@ -25885,7 +25864,7 @@
         <v>34128</v>
       </c>
       <c r="I506" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H506,TODAY(),"Y")</f>
       </c>
       <c r="J506" s="12"/>
       <c r="K506" s="13"/>
@@ -25921,7 +25900,7 @@
         <v>43218</v>
       </c>
       <c r="I507" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H507,TODAY(),"Y")</f>
       </c>
       <c r="J507" s="12"/>
       <c r="K507" s="13"/>
@@ -25957,7 +25936,7 @@
         <v>43651</v>
       </c>
       <c r="I508" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H508,TODAY(),"Y")</f>
       </c>
       <c r="J508" s="12"/>
       <c r="K508" s="13"/>
@@ -25993,7 +25972,7 @@
         <v>45264</v>
       </c>
       <c r="I509" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H509,TODAY(),"Y")</f>
       </c>
       <c r="J509" s="14"/>
       <c r="K509" s="11"/>
@@ -26029,7 +26008,7 @@
         <v>26801</v>
       </c>
       <c r="I510" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H510,TODAY(),"Y")</f>
       </c>
       <c r="J510" s="12">
         <v>0</v>
@@ -26071,7 +26050,7 @@
         <v>43552</v>
       </c>
       <c r="I511" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H511,TODAY(),"Y")</f>
       </c>
       <c r="J511" s="12"/>
       <c r="K511" s="13"/>
@@ -26107,7 +26086,7 @@
         <v>41415</v>
       </c>
       <c r="I512" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H512,TODAY(),"Y")</f>
       </c>
       <c r="J512" s="12"/>
       <c r="K512" s="13"/>
@@ -26143,7 +26122,7 @@
         <v>36988</v>
       </c>
       <c r="I513" s="5">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H513,TODAY(),"Y")</f>
       </c>
       <c r="J513" s="12"/>
       <c r="K513" s="13"/>
@@ -26179,7 +26158,7 @@
         <v>37177</v>
       </c>
       <c r="I514" s="9">
-        <f ca="1" t="shared" si="7"/>
+        <f>DATEDIF(H514,TODAY(),"Y")</f>
       </c>
       <c r="J514" s="12"/>
       <c r="K514" s="11"/>
@@ -26215,7 +26194,7 @@
         <v>37177</v>
       </c>
       <c r="I515" s="9">
-        <f ca="1" t="shared" ref="I515:I578" si="8">DATEDIF(H515,TODAY(),"Y")</f>
+        <f>DATEDIF(H515,TODAY(),"Y")</f>
       </c>
       <c r="J515" s="12"/>
       <c r="K515" s="13"/>
@@ -26251,7 +26230,7 @@
         <v>38947</v>
       </c>
       <c r="I516" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H516,TODAY(),"Y")</f>
       </c>
       <c r="J516" s="12"/>
       <c r="K516" s="13"/>
@@ -26287,7 +26266,7 @@
         <v>30120</v>
       </c>
       <c r="I517" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H517,TODAY(),"Y")</f>
       </c>
       <c r="J517" s="14">
         <v>1</v>
@@ -26329,7 +26308,7 @@
         <v>31910</v>
       </c>
       <c r="I518" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H518,TODAY(),"Y")</f>
       </c>
       <c r="J518" s="12"/>
       <c r="K518" s="13"/>
@@ -26365,7 +26344,7 @@
         <v>42181</v>
       </c>
       <c r="I519" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H519,TODAY(),"Y")</f>
       </c>
       <c r="J519" s="12"/>
       <c r="K519" s="13"/>
@@ -26403,7 +26382,7 @@
         <v>43564</v>
       </c>
       <c r="I520" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H520,TODAY(),"Y")</f>
       </c>
       <c r="J520" s="12"/>
       <c r="K520" s="13"/>
@@ -26439,7 +26418,7 @@
         <v>43564</v>
       </c>
       <c r="I521" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H521,TODAY(),"Y")</f>
       </c>
       <c r="J521" s="12"/>
       <c r="K521" s="13"/>
@@ -26475,7 +26454,7 @@
         <v>30793</v>
       </c>
       <c r="I522" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H522,TODAY(),"Y")</f>
       </c>
       <c r="J522" s="14">
         <v>0</v>
@@ -26517,7 +26496,7 @@
         <v>37446</v>
       </c>
       <c r="I523" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H523,TODAY(),"Y")</f>
       </c>
       <c r="J523" s="12"/>
       <c r="K523" s="13"/>
@@ -26553,7 +26532,7 @@
         <v>39568</v>
       </c>
       <c r="I524" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H524,TODAY(),"Y")</f>
       </c>
       <c r="J524" s="12"/>
       <c r="K524" s="13"/>
@@ -26589,7 +26568,7 @@
         <v>25429</v>
       </c>
       <c r="I525" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H525,TODAY(),"Y")</f>
       </c>
       <c r="J525" s="12">
         <v>1</v>
@@ -26631,7 +26610,7 @@
         <v>37404</v>
       </c>
       <c r="I526" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H526,TODAY(),"Y")</f>
       </c>
       <c r="J526" s="14"/>
       <c r="K526" s="11"/>
@@ -26667,7 +26646,7 @@
         <v>40311</v>
       </c>
       <c r="I527" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H527,TODAY(),"Y")</f>
       </c>
       <c r="J527" s="12"/>
       <c r="K527" s="13"/>
@@ -26703,7 +26682,7 @@
         <v>27096</v>
       </c>
       <c r="I528" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H528,TODAY(),"Y")</f>
       </c>
       <c r="J528" s="12"/>
       <c r="K528" s="13"/>
@@ -26739,7 +26718,7 @@
         <v>33784</v>
       </c>
       <c r="I529" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H529,TODAY(),"Y")</f>
       </c>
       <c r="J529" s="12">
         <v>0</v>
@@ -26781,7 +26760,7 @@
         <v>34015</v>
       </c>
       <c r="I530" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H530,TODAY(),"Y")</f>
       </c>
       <c r="J530" s="12">
         <v>1</v>
@@ -26823,7 +26802,7 @@
         <v>36078</v>
       </c>
       <c r="I531" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H531,TODAY(),"Y")</f>
       </c>
       <c r="J531" s="12"/>
       <c r="K531" s="13"/>
@@ -26859,7 +26838,7 @@
         <v>45227</v>
       </c>
       <c r="I532" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H532,TODAY(),"Y")</f>
       </c>
       <c r="J532" s="12"/>
       <c r="K532" s="13"/>
@@ -26895,7 +26874,7 @@
         <v>45836</v>
       </c>
       <c r="I533" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H533,TODAY(),"Y")</f>
       </c>
       <c r="J533" s="14"/>
       <c r="K533" s="15"/>
@@ -26931,7 +26910,7 @@
         <v>32528</v>
       </c>
       <c r="I534" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H534,TODAY(),"Y")</f>
       </c>
       <c r="J534" s="12">
         <v>1</v>
@@ -26973,7 +26952,7 @@
         <v>33805</v>
       </c>
       <c r="I535" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H535,TODAY(),"Y")</f>
       </c>
       <c r="J535" s="12"/>
       <c r="K535" s="13"/>
@@ -27009,7 +26988,7 @@
         <v>44325</v>
       </c>
       <c r="I536" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H536,TODAY(),"Y")</f>
       </c>
       <c r="J536" s="14"/>
       <c r="K536" s="11"/>
@@ -27045,7 +27024,7 @@
         <v>30317</v>
       </c>
       <c r="I537" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H537,TODAY(),"Y")</f>
       </c>
       <c r="J537" s="12">
         <v>0</v>
@@ -27087,7 +27066,7 @@
         <v>42865</v>
       </c>
       <c r="I538" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H538,TODAY(),"Y")</f>
       </c>
       <c r="J538" s="12"/>
       <c r="K538" s="13"/>
@@ -27123,7 +27102,7 @@
         <v>43708</v>
       </c>
       <c r="I539" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H539,TODAY(),"Y")</f>
       </c>
       <c r="J539" s="12"/>
       <c r="K539" s="13"/>
@@ -27159,7 +27138,7 @@
         <v>45756</v>
       </c>
       <c r="I540" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H540,TODAY(),"Y")</f>
       </c>
       <c r="J540" s="12"/>
       <c r="K540" s="13"/>
@@ -27195,7 +27174,7 @@
         <v>35574</v>
       </c>
       <c r="I541" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H541,TODAY(),"Y")</f>
       </c>
       <c r="J541" s="12">
         <v>1</v>
@@ -27237,7 +27216,7 @@
         <v>34207</v>
       </c>
       <c r="I542" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H542,TODAY(),"Y")</f>
       </c>
       <c r="J542" s="14"/>
       <c r="K542" s="11"/>
@@ -27273,7 +27252,7 @@
         <v>46006</v>
       </c>
       <c r="I543" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H543,TODAY(),"Y")</f>
       </c>
       <c r="J543" s="12"/>
       <c r="K543" s="13"/>
@@ -27309,7 +27288,7 @@
         <v>28626</v>
       </c>
       <c r="I544" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H544,TODAY(),"Y")</f>
       </c>
       <c r="J544" s="12">
         <v>1</v>
@@ -27351,7 +27330,7 @@
         <v>39949</v>
       </c>
       <c r="I545" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H545,TODAY(),"Y")</f>
       </c>
       <c r="J545" s="12"/>
       <c r="K545" s="13"/>
@@ -27387,7 +27366,7 @@
         <v>44577</v>
       </c>
       <c r="I546" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H546,TODAY(),"Y")</f>
       </c>
       <c r="J546" s="12"/>
       <c r="K546" s="13"/>
@@ -27423,7 +27402,7 @@
         <v>44934</v>
       </c>
       <c r="I547" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H547,TODAY(),"Y")</f>
       </c>
       <c r="J547" s="12"/>
       <c r="K547" s="13"/>
@@ -27459,7 +27438,7 @@
         <v>35115</v>
       </c>
       <c r="I548" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H548,TODAY(),"Y")</f>
       </c>
       <c r="J548" s="14"/>
       <c r="K548" s="11"/>
@@ -27495,7 +27474,7 @@
         <v>32694</v>
       </c>
       <c r="I549" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H549,TODAY(),"Y")</f>
       </c>
       <c r="J549" s="12">
         <v>1</v>
@@ -27537,7 +27516,7 @@
         <v>34541</v>
       </c>
       <c r="I550" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H550,TODAY(),"Y")</f>
       </c>
       <c r="J550" s="12"/>
       <c r="K550" s="13"/>
@@ -27573,7 +27552,7 @@
         <v>43147</v>
       </c>
       <c r="I551" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H551,TODAY(),"Y")</f>
       </c>
       <c r="J551" s="12"/>
       <c r="K551" s="13"/>
@@ -27609,7 +27588,7 @@
         <v>39860</v>
       </c>
       <c r="I552" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H552,TODAY(),"Y")</f>
       </c>
       <c r="J552" s="14"/>
       <c r="K552" s="15"/>
@@ -27645,7 +27624,7 @@
         <v>45178</v>
       </c>
       <c r="I553" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H553,TODAY(),"Y")</f>
       </c>
       <c r="J553" s="12"/>
       <c r="K553" s="13"/>
@@ -27681,7 +27660,7 @@
         <v>45858</v>
       </c>
       <c r="I554" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H554,TODAY(),"Y")</f>
       </c>
       <c r="J554" s="12"/>
       <c r="K554" s="11"/>
@@ -27717,7 +27696,7 @@
         <v>32373</v>
       </c>
       <c r="I555" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H555,TODAY(),"Y")</f>
       </c>
       <c r="J555" s="12">
         <v>1</v>
@@ -27759,7 +27738,7 @@
         <v>33604</v>
       </c>
       <c r="I556" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H556,TODAY(),"Y")</f>
       </c>
       <c r="J556" s="14"/>
       <c r="K556" s="11"/>
@@ -27795,7 +27774,7 @@
         <v>43132</v>
       </c>
       <c r="I557" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H557,TODAY(),"Y")</f>
       </c>
       <c r="J557" s="12"/>
       <c r="K557" s="13"/>
@@ -27831,7 +27810,7 @@
         <v>44259</v>
       </c>
       <c r="I558" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H558,TODAY(),"Y")</f>
       </c>
       <c r="J558" s="12"/>
       <c r="K558" s="13"/>
@@ -27867,7 +27846,7 @@
         <v>29317</v>
       </c>
       <c r="I559" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H559,TODAY(),"Y")</f>
       </c>
       <c r="J559" s="12">
         <v>1</v>
@@ -27909,7 +27888,7 @@
         <v>34172</v>
       </c>
       <c r="I560" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H560,TODAY(),"Y")</f>
       </c>
       <c r="J560" s="12"/>
       <c r="K560" s="13"/>
@@ -27945,7 +27924,7 @@
         <v>35522</v>
       </c>
       <c r="I561" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H561,TODAY(),"Y")</f>
       </c>
       <c r="J561" s="14">
         <v>0</v>
@@ -27987,7 +27966,7 @@
         <v>45902</v>
       </c>
       <c r="I562" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H562,TODAY(),"Y")</f>
       </c>
       <c r="J562" s="12"/>
       <c r="K562" s="13"/>
@@ -28023,7 +28002,7 @@
         <v>29902</v>
       </c>
       <c r="I563" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H563,TODAY(),"Y")</f>
       </c>
       <c r="J563" s="14">
         <v>1</v>
@@ -28065,7 +28044,7 @@
         <v>31542</v>
       </c>
       <c r="I564" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H564,TODAY(),"Y")</f>
       </c>
       <c r="J564" s="12"/>
       <c r="K564" s="13"/>
@@ -28101,7 +28080,7 @@
         <v>41661</v>
       </c>
       <c r="I565" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H565,TODAY(),"Y")</f>
       </c>
       <c r="J565" s="12"/>
       <c r="K565" s="13"/>
@@ -28137,7 +28116,7 @@
         <v>45989</v>
       </c>
       <c r="I566" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H566,TODAY(),"Y")</f>
       </c>
       <c r="J566" s="12"/>
       <c r="K566" s="13"/>
@@ -28175,7 +28154,7 @@
         <v>34103</v>
       </c>
       <c r="I567" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H567,TODAY(),"Y")</f>
       </c>
       <c r="J567" s="12">
         <v>0</v>
@@ -28217,7 +28196,7 @@
         <v>32865</v>
       </c>
       <c r="I568" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H568,TODAY(),"Y")</f>
       </c>
       <c r="J568" s="12">
         <v>0</v>
@@ -28259,7 +28238,7 @@
         <v>31767</v>
       </c>
       <c r="I569" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H569,TODAY(),"Y")</f>
       </c>
       <c r="J569" s="12">
         <v>1</v>
@@ -28301,7 +28280,7 @@
         <v>35603</v>
       </c>
       <c r="I570" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H570,TODAY(),"Y")</f>
       </c>
       <c r="J570" s="12"/>
       <c r="K570" s="13"/>
@@ -28337,7 +28316,7 @@
         <v>46001</v>
       </c>
       <c r="I571" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H571,TODAY(),"Y")</f>
       </c>
       <c r="J571" s="12"/>
       <c r="K571" s="13"/>
@@ -28375,7 +28354,7 @@
         <v>28711</v>
       </c>
       <c r="I572" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H572,TODAY(),"Y")</f>
       </c>
       <c r="J572" s="12">
         <v>1</v>
@@ -28417,7 +28396,7 @@
         <v>31988</v>
       </c>
       <c r="I573" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H573,TODAY(),"Y")</f>
       </c>
       <c r="J573" s="14"/>
       <c r="K573" s="11"/>
@@ -28453,7 +28432,7 @@
         <v>39611</v>
       </c>
       <c r="I574" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H574,TODAY(),"Y")</f>
       </c>
       <c r="J574" s="12"/>
       <c r="K574" s="13"/>
@@ -28489,7 +28468,7 @@
         <v>40116</v>
       </c>
       <c r="I575" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H575,TODAY(),"Y")</f>
       </c>
       <c r="J575" s="12"/>
       <c r="K575" s="13"/>
@@ -28525,7 +28504,7 @@
         <v>40658</v>
       </c>
       <c r="I576" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H576,TODAY(),"Y")</f>
       </c>
       <c r="J576" s="12"/>
       <c r="K576" s="13"/>
@@ -28561,7 +28540,7 @@
         <v>41881</v>
       </c>
       <c r="I577" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H577,TODAY(),"Y")</f>
       </c>
       <c r="J577" s="12"/>
       <c r="K577" s="13"/>
@@ -28597,7 +28576,7 @@
         <v>42386</v>
       </c>
       <c r="I578" s="9">
-        <f ca="1" t="shared" si="8"/>
+        <f>DATEDIF(H578,TODAY(),"Y")</f>
       </c>
       <c r="J578" s="14"/>
       <c r="K578" s="15"/>
@@ -28633,7 +28612,7 @@
         <v>43090</v>
       </c>
       <c r="I579" s="9">
-        <f ca="1" t="shared" ref="I579:I642" si="9">DATEDIF(H579,TODAY(),"Y")</f>
+        <f>DATEDIF(H579,TODAY(),"Y")</f>
       </c>
       <c r="J579" s="12"/>
       <c r="K579" s="13"/>
@@ -28669,7 +28648,7 @@
         <v>43536</v>
       </c>
       <c r="I580" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H580,TODAY(),"Y")</f>
       </c>
       <c r="J580" s="14"/>
       <c r="K580" s="11"/>
@@ -28705,7 +28684,7 @@
         <v>44613</v>
       </c>
       <c r="I581" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H581,TODAY(),"Y")</f>
       </c>
       <c r="J581" s="12"/>
       <c r="K581" s="13"/>
@@ -28741,7 +28720,7 @@
         <v>31779</v>
       </c>
       <c r="I582" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H582,TODAY(),"Y")</f>
       </c>
       <c r="J582" s="12">
         <v>1</v>
@@ -28783,7 +28762,7 @@
         <v>44343</v>
       </c>
       <c r="I583" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H583,TODAY(),"Y")</f>
       </c>
       <c r="J583" s="12"/>
       <c r="K583" s="13"/>
@@ -28819,7 +28798,7 @@
         <v>33862</v>
       </c>
       <c r="I584" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H584,TODAY(),"Y")</f>
       </c>
       <c r="J584" s="12"/>
       <c r="K584" s="13"/>
@@ -28855,7 +28834,7 @@
         <v>45313</v>
       </c>
       <c r="I585" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H585,TODAY(),"Y")</f>
       </c>
       <c r="J585" s="14"/>
       <c r="K585" s="11"/>
@@ -28891,7 +28870,7 @@
         <v>45878</v>
       </c>
       <c r="I586" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H586,TODAY(),"Y")</f>
       </c>
       <c r="J586" s="12"/>
       <c r="K586" s="13"/>
@@ -28927,7 +28906,7 @@
         <v>35969</v>
       </c>
       <c r="I587" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H587,TODAY(),"Y")</f>
       </c>
       <c r="J587" s="12">
         <v>0</v>
@@ -28969,7 +28948,7 @@
         <v>45981</v>
       </c>
       <c r="I588" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H588,TODAY(),"Y")</f>
       </c>
       <c r="J588" s="14"/>
       <c r="K588" s="11"/>
@@ -29005,7 +28984,7 @@
         <v>31613</v>
       </c>
       <c r="I589" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H589,TODAY(),"Y")</f>
       </c>
       <c r="J589" s="12">
         <v>1</v>
@@ -29047,7 +29026,7 @@
         <v>34208</v>
       </c>
       <c r="I590" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H590,TODAY(),"Y")</f>
       </c>
       <c r="J590" s="12"/>
       <c r="K590" s="13"/>
@@ -29083,7 +29062,7 @@
         <v>42636</v>
       </c>
       <c r="I591" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H591,TODAY(),"Y")</f>
       </c>
       <c r="J591" s="12"/>
       <c r="K591" s="13"/>
@@ -29119,7 +29098,7 @@
         <v>44210</v>
       </c>
       <c r="I592" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H592,TODAY(),"Y")</f>
       </c>
       <c r="J592" s="12"/>
       <c r="K592" s="13"/>
@@ -29155,7 +29134,7 @@
         <v>43641</v>
       </c>
       <c r="I593" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H593,TODAY(),"Y")</f>
       </c>
       <c r="J593" s="12"/>
       <c r="K593" s="13"/>
@@ -29191,7 +29170,7 @@
         <v>33937</v>
       </c>
       <c r="I594" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H594,TODAY(),"Y")</f>
       </c>
       <c r="J594" s="12">
         <v>1</v>
@@ -29233,7 +29212,7 @@
         <v>35058</v>
       </c>
       <c r="I595" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H595,TODAY(),"Y")</f>
       </c>
       <c r="J595" s="14"/>
       <c r="K595" s="11"/>
@@ -29269,7 +29248,7 @@
         <v>44411</v>
       </c>
       <c r="I596" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H596,TODAY(),"Y")</f>
       </c>
       <c r="J596" s="12"/>
       <c r="K596" s="13"/>
@@ -29305,7 +29284,7 @@
         <v>30279</v>
       </c>
       <c r="I597" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H597,TODAY(),"Y")</f>
       </c>
       <c r="J597" s="12">
         <v>1</v>
@@ -29347,7 +29326,7 @@
         <v>32108</v>
       </c>
       <c r="I598" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H598,TODAY(),"Y")</f>
       </c>
       <c r="J598" s="14"/>
       <c r="K598" s="11"/>
@@ -29383,7 +29362,7 @@
         <v>44783</v>
       </c>
       <c r="I599" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H599,TODAY(),"Y")</f>
       </c>
       <c r="J599" s="12"/>
       <c r="K599" s="13"/>
@@ -29419,7 +29398,7 @@
         <v>41427</v>
       </c>
       <c r="I600" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H600,TODAY(),"Y")</f>
       </c>
       <c r="J600" s="12"/>
       <c r="K600" s="13"/>
@@ -29455,7 +29434,7 @@
         <v>42312</v>
       </c>
       <c r="I601" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H601,TODAY(),"Y")</f>
       </c>
       <c r="J601" s="12"/>
       <c r="K601" s="13"/>
@@ -29491,7 +29470,7 @@
         <v>43824</v>
       </c>
       <c r="I602" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H602,TODAY(),"Y")</f>
       </c>
       <c r="J602" s="12"/>
       <c r="K602" s="13"/>
@@ -29527,7 +29506,7 @@
         <v>45512</v>
       </c>
       <c r="I603" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H603,TODAY(),"Y")</f>
       </c>
       <c r="J603" s="12"/>
       <c r="K603" s="13"/>
@@ -29563,7 +29542,7 @@
         <v>34414</v>
       </c>
       <c r="I604" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H604,TODAY(),"Y")</f>
       </c>
       <c r="J604" s="12">
         <v>1</v>
@@ -29605,7 +29584,7 @@
         <v>36294</v>
       </c>
       <c r="I605" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H605,TODAY(),"Y")</f>
       </c>
       <c r="J605" s="14"/>
       <c r="K605" s="15"/>
@@ -29641,7 +29620,7 @@
         <v>45934</v>
       </c>
       <c r="I606" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H606,TODAY(),"Y")</f>
       </c>
       <c r="J606" s="14"/>
       <c r="K606" s="15"/>
@@ -29677,7 +29656,7 @@
         <v>30520</v>
       </c>
       <c r="I607" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H607,TODAY(),"Y")</f>
       </c>
       <c r="J607" s="14">
         <v>1</v>
@@ -29719,7 +29698,7 @@
         <v>30177</v>
       </c>
       <c r="I608" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H608,TODAY(),"Y")</f>
       </c>
       <c r="J608" s="12"/>
       <c r="K608" s="13"/>
@@ -29755,7 +29734,7 @@
         <v>45097</v>
       </c>
       <c r="I609" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H609,TODAY(),"Y")</f>
       </c>
       <c r="J609" s="14"/>
       <c r="K609" s="11"/>
@@ -29791,7 +29770,7 @@
         <v>43343</v>
       </c>
       <c r="I610" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H610,TODAY(),"Y")</f>
       </c>
       <c r="J610" s="14"/>
       <c r="K610" s="15"/>
@@ -29827,7 +29806,7 @@
         <v>41870</v>
       </c>
       <c r="I611" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H611,TODAY(),"Y")</f>
       </c>
       <c r="J611" s="14"/>
       <c r="K611" s="15"/>
@@ -29863,7 +29842,7 @@
         <v>41384</v>
       </c>
       <c r="I612" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H612,TODAY(),"Y")</f>
       </c>
       <c r="J612" s="14"/>
       <c r="K612" s="15"/>
@@ -29899,7 +29878,7 @@
         <v>40669</v>
       </c>
       <c r="I613" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H613,TODAY(),"Y")</f>
       </c>
       <c r="J613" s="14"/>
       <c r="K613" s="11"/>
@@ -29935,7 +29914,7 @@
         <v>35066</v>
       </c>
       <c r="I614" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H614,TODAY(),"Y")</f>
       </c>
       <c r="J614" s="14">
         <v>1</v>
@@ -29977,7 +29956,7 @@
         <v>35867</v>
       </c>
       <c r="I615" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H615,TODAY(),"Y")</f>
       </c>
       <c r="J615" s="14"/>
       <c r="K615" s="15"/>
@@ -30013,7 +29992,7 @@
         <v>32041</v>
       </c>
       <c r="I616" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H616,TODAY(),"Y")</f>
       </c>
       <c r="J616" s="14">
         <v>1</v>
@@ -30055,7 +30034,7 @@
         <v>36639</v>
       </c>
       <c r="I617" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H617,TODAY(),"Y")</f>
       </c>
       <c r="J617" s="14"/>
       <c r="K617" s="11"/>
@@ -30091,7 +30070,7 @@
         <v>32653</v>
       </c>
       <c r="I618" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H618,TODAY(),"Y")</f>
       </c>
       <c r="J618" s="12">
         <v>1</v>
@@ -30133,7 +30112,7 @@
         <v>33405</v>
       </c>
       <c r="I619" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H619,TODAY(),"Y")</f>
       </c>
       <c r="J619" s="12"/>
       <c r="K619" s="13"/>
@@ -30169,7 +30148,7 @@
         <v>44387</v>
       </c>
       <c r="I620" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H620,TODAY(),"Y")</f>
       </c>
       <c r="J620" s="12"/>
       <c r="K620" s="13"/>
@@ -30205,7 +30184,7 @@
         <v>40102</v>
       </c>
       <c r="I621" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H621,TODAY(),"Y")</f>
       </c>
       <c r="J621" s="12"/>
       <c r="K621" s="13"/>
@@ -30243,7 +30222,7 @@
         <v>35285</v>
       </c>
       <c r="I622" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H622,TODAY(),"Y")</f>
       </c>
       <c r="J622" s="12">
         <v>1</v>
@@ -30285,7 +30264,7 @@
         <v>35450</v>
       </c>
       <c r="I623" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H623,TODAY(),"Y")</f>
       </c>
       <c r="J623" s="12"/>
       <c r="K623" s="13"/>
@@ -30321,7 +30300,7 @@
         <v>45048</v>
       </c>
       <c r="I624" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H624,TODAY(),"Y")</f>
       </c>
       <c r="J624" s="14"/>
       <c r="K624" s="11"/>
@@ -30357,7 +30336,7 @@
         <v>46190</v>
       </c>
       <c r="I625" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H625,TODAY(),"Y")</f>
       </c>
       <c r="J625" s="12"/>
       <c r="K625" s="13"/>
@@ -30395,7 +30374,7 @@
         <v>36806</v>
       </c>
       <c r="I626" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H626,TODAY(),"Y")</f>
       </c>
       <c r="J626" s="12">
         <v>0</v>
@@ -30437,7 +30416,7 @@
         <v>31578</v>
       </c>
       <c r="I627" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H627,TODAY(),"Y")</f>
       </c>
       <c r="J627" s="12">
         <v>1</v>
@@ -30479,7 +30458,7 @@
         <v>32830</v>
       </c>
       <c r="I628" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H628,TODAY(),"Y")</f>
       </c>
       <c r="J628" s="14"/>
       <c r="K628" s="15"/>
@@ -30515,7 +30494,7 @@
         <v>44802</v>
       </c>
       <c r="I629" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H629,TODAY(),"Y")</f>
       </c>
       <c r="J629" s="14"/>
       <c r="K629" s="15"/>
@@ -30551,7 +30530,7 @@
         <v>34429</v>
       </c>
       <c r="I630" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H630,TODAY(),"Y")</f>
       </c>
       <c r="J630" s="14">
         <v>0</v>
@@ -30593,7 +30572,7 @@
         <v>35114</v>
       </c>
       <c r="I631" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H631,TODAY(),"Y")</f>
       </c>
       <c r="J631" s="14">
         <v>0</v>
@@ -30635,7 +30614,7 @@
         <v>36498</v>
       </c>
       <c r="I632" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H632,TODAY(),"Y")</f>
       </c>
       <c r="J632" s="14">
         <v>0</v>
@@ -30677,7 +30656,7 @@
         <v>34268</v>
       </c>
       <c r="I633" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H633,TODAY(),"Y")</f>
       </c>
       <c r="J633" s="14">
         <v>1</v>
@@ -30719,7 +30698,7 @@
         <v>35488</v>
       </c>
       <c r="I634" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H634,TODAY(),"Y")</f>
       </c>
       <c r="J634" s="14"/>
       <c r="K634" s="15"/>
@@ -30755,7 +30734,7 @@
         <v>45113</v>
       </c>
       <c r="I635" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H635,TODAY(),"Y")</f>
       </c>
       <c r="J635" s="14"/>
       <c r="K635" s="11"/>
@@ -30791,7 +30770,7 @@
         <v>45812</v>
       </c>
       <c r="I636" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H636,TODAY(),"Y")</f>
       </c>
       <c r="J636" s="12"/>
       <c r="K636" s="13"/>
@@ -30827,7 +30806,7 @@
         <v>35765</v>
       </c>
       <c r="I637" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H637,TODAY(),"Y")</f>
       </c>
       <c r="J637" s="12">
         <v>0</v>
@@ -30869,7 +30848,7 @@
         <v>36150</v>
       </c>
       <c r="I638" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H638,TODAY(),"Y")</f>
       </c>
       <c r="J638" s="12">
         <v>0</v>
@@ -30911,7 +30890,7 @@
         <v>36231</v>
       </c>
       <c r="I639" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H639,TODAY(),"Y")</f>
       </c>
       <c r="J639" s="14">
         <v>0</v>
@@ -30953,7 +30932,7 @@
         <v>30476</v>
       </c>
       <c r="I640" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H640,TODAY(),"Y")</f>
       </c>
       <c r="J640" s="14">
         <v>0</v>
@@ -30995,7 +30974,7 @@
         <v>34844</v>
       </c>
       <c r="I641" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H641,TODAY(),"Y")</f>
       </c>
       <c r="J641" s="14">
         <v>0</v>
@@ -31037,7 +31016,7 @@
         <v>34439</v>
       </c>
       <c r="I642" s="9">
-        <f ca="1" t="shared" si="9"/>
+        <f>DATEDIF(H642,TODAY(),"Y")</f>
       </c>
       <c r="J642" s="14">
         <v>0</v>
@@ -31079,7 +31058,7 @@
         <v>34128</v>
       </c>
       <c r="I643" s="9">
-        <f ca="1" t="shared" ref="I643:I706" si="10">DATEDIF(H643,TODAY(),"Y")</f>
+        <f>DATEDIF(H643,TODAY(),"Y")</f>
       </c>
       <c r="J643" s="14">
         <v>0</v>
@@ -31121,7 +31100,7 @@
         <v>30463</v>
       </c>
       <c r="I644" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H644,TODAY(),"Y")</f>
       </c>
       <c r="J644" s="14">
         <v>1</v>
@@ -31163,7 +31142,7 @@
         <v>31260</v>
       </c>
       <c r="I645" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H645,TODAY(),"Y")</f>
       </c>
       <c r="J645" s="14"/>
       <c r="K645" s="15"/>
@@ -31199,7 +31178,7 @@
         <v>42313</v>
       </c>
       <c r="I646" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H646,TODAY(),"Y")</f>
       </c>
       <c r="J646" s="14"/>
       <c r="K646" s="15"/>
@@ -31235,7 +31214,7 @@
         <v>45532</v>
       </c>
       <c r="I647" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H647,TODAY(),"Y")</f>
       </c>
       <c r="J647" s="14"/>
       <c r="K647" s="15"/>
@@ -31271,7 +31250,7 @@
         <v>37476</v>
       </c>
       <c r="I648" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H648,TODAY(),"Y")</f>
       </c>
       <c r="J648" s="14">
         <v>0</v>
@@ -31313,7 +31292,7 @@
         <v>34339</v>
       </c>
       <c r="I649" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H649,TODAY(),"Y")</f>
       </c>
       <c r="J649" s="14">
         <v>0</v>
@@ -31355,7 +31334,7 @@
         <v>41981</v>
       </c>
       <c r="I650" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H650,TODAY(),"Y")</f>
       </c>
       <c r="J650" s="14"/>
       <c r="K650" s="11"/>
@@ -31391,7 +31370,7 @@
         <v>41269</v>
       </c>
       <c r="I651" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H651,TODAY(),"Y")</f>
       </c>
       <c r="J651" s="14"/>
       <c r="K651" s="15"/>
@@ -31427,7 +31406,7 @@
         <v>36193</v>
       </c>
       <c r="I652" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H652,TODAY(),"Y")</f>
       </c>
       <c r="J652" s="14">
         <v>0</v>
@@ -31469,7 +31448,7 @@
         <v>30946</v>
       </c>
       <c r="I653" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H653,TODAY(),"Y")</f>
       </c>
       <c r="J653" s="14">
         <v>1</v>
@@ -31511,7 +31490,7 @@
         <v>33370</v>
       </c>
       <c r="I654" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H654,TODAY(),"Y")</f>
       </c>
       <c r="J654" s="14"/>
       <c r="K654" s="11"/>
@@ -31547,7 +31526,7 @@
         <v>42498</v>
       </c>
       <c r="I655" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H655,TODAY(),"Y")</f>
       </c>
       <c r="J655" s="14"/>
       <c r="K655" s="15"/>
@@ -31583,7 +31562,7 @@
         <v>43010</v>
       </c>
       <c r="I656" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H656,TODAY(),"Y")</f>
       </c>
       <c r="J656" s="14"/>
       <c r="K656" s="15"/>
@@ -31619,7 +31598,7 @@
         <v>43488</v>
       </c>
       <c r="I657" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H657,TODAY(),"Y")</f>
       </c>
       <c r="J657" s="14"/>
       <c r="K657" s="11"/>
@@ -31655,7 +31634,7 @@
         <v>45642</v>
       </c>
       <c r="I658" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H658,TODAY(),"Y")</f>
       </c>
       <c r="J658" s="14"/>
       <c r="K658" s="15"/>
@@ -31691,7 +31670,7 @@
         <v>33031</v>
       </c>
       <c r="I659" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H659,TODAY(),"Y")</f>
       </c>
       <c r="J659" s="14">
         <v>1</v>
@@ -31733,7 +31712,7 @@
         <v>43261</v>
       </c>
       <c r="I660" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H660,TODAY(),"Y")</f>
       </c>
       <c r="J660" s="14"/>
       <c r="K660" s="15"/>
@@ -31769,7 +31748,7 @@
         <v>34007</v>
       </c>
       <c r="I661" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H661,TODAY(),"Y")</f>
       </c>
       <c r="J661" s="14"/>
       <c r="K661" s="15"/>
@@ -31805,7 +31784,7 @@
         <v>44702</v>
       </c>
       <c r="I662" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H662,TODAY(),"Y")</f>
       </c>
       <c r="J662" s="14"/>
       <c r="K662" s="11"/>
@@ -31841,7 +31820,7 @@
         <v>33290</v>
       </c>
       <c r="I663" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H663,TODAY(),"Y")</f>
       </c>
       <c r="J663" s="14">
         <v>1</v>
@@ -31883,7 +31862,7 @@
         <v>35867</v>
       </c>
       <c r="I664" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H664,TODAY(),"Y")</f>
       </c>
       <c r="J664" s="14"/>
       <c r="K664" s="15"/>
@@ -31919,7 +31898,7 @@
         <v>45731</v>
       </c>
       <c r="I665" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H665,TODAY(),"Y")</f>
       </c>
       <c r="J665" s="14"/>
       <c r="K665" s="15"/>
@@ -31955,7 +31934,7 @@
         <v>32351</v>
       </c>
       <c r="I666" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H666,TODAY(),"Y")</f>
       </c>
       <c r="J666" s="14">
         <v>1</v>
@@ -31997,7 +31976,7 @@
         <v>34328</v>
       </c>
       <c r="I667" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H667,TODAY(),"Y")</f>
       </c>
       <c r="J667" s="14"/>
       <c r="K667" s="15"/>
@@ -32033,7 +32012,7 @@
         <v>45206</v>
       </c>
       <c r="I668" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H668,TODAY(),"Y")</f>
       </c>
       <c r="J668" s="14"/>
       <c r="K668" s="15"/>
@@ -32069,7 +32048,7 @@
         <v>45615</v>
       </c>
       <c r="I669" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H669,TODAY(),"Y")</f>
       </c>
       <c r="J669" s="14"/>
       <c r="K669" s="15"/>
@@ -32105,7 +32084,7 @@
         <v>36151</v>
       </c>
       <c r="I670" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H670,TODAY(),"Y")</f>
       </c>
       <c r="J670" s="14">
         <v>0</v>
@@ -32147,7 +32126,7 @@
         <v>30744</v>
       </c>
       <c r="I671" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H671,TODAY(),"Y")</f>
       </c>
       <c r="J671" s="14">
         <v>1</v>
@@ -32189,7 +32168,7 @@
         <v>33209</v>
       </c>
       <c r="I672" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H672,TODAY(),"Y")</f>
       </c>
       <c r="J672" s="14"/>
       <c r="K672" s="11"/>
@@ -32225,7 +32204,7 @@
         <v>40443</v>
       </c>
       <c r="I673" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H673,TODAY(),"Y")</f>
       </c>
       <c r="J673" s="14"/>
       <c r="K673" s="15"/>
@@ -32261,7 +32240,7 @@
         <v>41053</v>
       </c>
       <c r="I674" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H674,TODAY(),"Y")</f>
       </c>
       <c r="J674" s="14"/>
       <c r="K674" s="15"/>
@@ -32297,7 +32276,7 @@
         <v>42487</v>
       </c>
       <c r="I675" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H675,TODAY(),"Y")</f>
       </c>
       <c r="J675" s="14"/>
       <c r="K675" s="15"/>
@@ -32333,7 +32312,7 @@
         <v>43431</v>
       </c>
       <c r="I676" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H676,TODAY(),"Y")</f>
       </c>
       <c r="J676" s="14"/>
       <c r="K676" s="11"/>
@@ -32369,7 +32348,7 @@
         <v>44211</v>
       </c>
       <c r="I677" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H677,TODAY(),"Y")</f>
       </c>
       <c r="J677" s="14"/>
       <c r="K677" s="15"/>
@@ -32405,7 +32384,7 @@
         <v>45721</v>
       </c>
       <c r="I678" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H678,TODAY(),"Y")</f>
       </c>
       <c r="J678" s="14"/>
       <c r="K678" s="15"/>
@@ -32441,7 +32420,7 @@
         <v>45721</v>
       </c>
       <c r="I679" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H679,TODAY(),"Y")</f>
       </c>
       <c r="J679" s="14"/>
       <c r="K679" s="15"/>
@@ -32477,7 +32456,7 @@
         <v>32093</v>
       </c>
       <c r="I680" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H680,TODAY(),"Y")</f>
       </c>
       <c r="J680" s="14">
         <v>0</v>
@@ -32519,7 +32498,7 @@
         <v>28839</v>
       </c>
       <c r="I681" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H681,TODAY(),"Y")</f>
       </c>
       <c r="J681" s="14">
         <v>1</v>
@@ -32561,7 +32540,7 @@
         <v>29794</v>
       </c>
       <c r="I682" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H682,TODAY(),"Y")</f>
       </c>
       <c r="J682" s="14"/>
       <c r="K682" s="15"/>
@@ -32597,7 +32576,7 @@
         <v>42075</v>
       </c>
       <c r="I683" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H683,TODAY(),"Y")</f>
       </c>
       <c r="J683" s="14"/>
       <c r="K683" s="15"/>
@@ -32633,7 +32612,7 @@
         <v>40581</v>
       </c>
       <c r="I684" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H684,TODAY(),"Y")</f>
       </c>
       <c r="J684" s="14"/>
       <c r="K684" s="15"/>
@@ -32669,7 +32648,7 @@
         <v>34417</v>
       </c>
       <c r="I685" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H685,TODAY(),"Y")</f>
       </c>
       <c r="J685" s="14">
         <v>1</v>
@@ -32711,7 +32690,7 @@
         <v>34580</v>
       </c>
       <c r="I686" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H686,TODAY(),"Y")</f>
       </c>
       <c r="J686" s="14"/>
       <c r="K686" s="15"/>
@@ -32747,7 +32726,7 @@
         <v>45695</v>
       </c>
       <c r="I687" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H687,TODAY(),"Y")</f>
       </c>
       <c r="J687" s="14"/>
       <c r="K687" s="15"/>
@@ -32783,7 +32762,7 @@
         <v>45394</v>
       </c>
       <c r="I688" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H688,TODAY(),"Y")</f>
       </c>
       <c r="J688" s="14"/>
       <c r="K688" s="15"/>
@@ -32819,7 +32798,7 @@
         <v>32689</v>
       </c>
       <c r="I689" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H689,TODAY(),"Y")</f>
       </c>
       <c r="J689" s="14">
         <v>1</v>
@@ -32861,7 +32840,7 @@
         <v>33853</v>
       </c>
       <c r="I690" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H690,TODAY(),"Y")</f>
       </c>
       <c r="J690" s="14"/>
       <c r="K690" s="15"/>
@@ -32897,7 +32876,7 @@
         <v>43299</v>
       </c>
       <c r="I691" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H691,TODAY(),"Y")</f>
       </c>
       <c r="J691" s="14"/>
       <c r="K691" s="15"/>
@@ -32933,7 +32912,7 @@
         <v>44427</v>
       </c>
       <c r="I692" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H692,TODAY(),"Y")</f>
       </c>
       <c r="J692" s="14"/>
       <c r="K692" s="15"/>
@@ -32969,7 +32948,7 @@
         <v>45661</v>
       </c>
       <c r="I693" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H693,TODAY(),"Y")</f>
       </c>
       <c r="J693" s="14"/>
       <c r="K693" s="15"/>
@@ -33005,7 +32984,7 @@
         <v>30494</v>
       </c>
       <c r="I694" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H694,TODAY(),"Y")</f>
       </c>
       <c r="J694" s="14">
         <v>0</v>
@@ -33047,7 +33026,7 @@
         <v>40836</v>
       </c>
       <c r="I695" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H695,TODAY(),"Y")</f>
       </c>
       <c r="J695" s="14"/>
       <c r="K695" s="11"/>
@@ -33083,7 +33062,7 @@
         <v>39810</v>
       </c>
       <c r="I696" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H696,TODAY(),"Y")</f>
       </c>
       <c r="J696" s="14"/>
       <c r="K696" s="15"/>
@@ -33119,7 +33098,7 @@
         <v>39227</v>
       </c>
       <c r="I697" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H697,TODAY(),"Y")</f>
       </c>
       <c r="J697" s="14"/>
       <c r="K697" s="15"/>
@@ -33155,7 +33134,7 @@
         <v>36210</v>
       </c>
       <c r="I698" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H698,TODAY(),"Y")</f>
       </c>
       <c r="J698" s="14">
         <v>0</v>
@@ -33197,7 +33176,7 @@
         <v>33260</v>
       </c>
       <c r="I699" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H699,TODAY(),"Y")</f>
       </c>
       <c r="J699" s="14">
         <v>1</v>
@@ -33239,7 +33218,7 @@
         <v>35055</v>
       </c>
       <c r="I700" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H700,TODAY(),"Y")</f>
       </c>
       <c r="J700" s="14"/>
       <c r="K700" s="11"/>
@@ -33275,7 +33254,7 @@
         <v>43062</v>
       </c>
       <c r="I701" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H701,TODAY(),"Y")</f>
       </c>
       <c r="J701" s="12"/>
       <c r="K701" s="13"/>
@@ -33311,7 +33290,7 @@
         <v>44177</v>
       </c>
       <c r="I702" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H702,TODAY(),"Y")</f>
       </c>
       <c r="J702" s="12"/>
       <c r="K702" s="13"/>
@@ -33347,7 +33326,7 @@
         <v>43605</v>
       </c>
       <c r="I703" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H703,TODAY(),"Y")</f>
       </c>
       <c r="J703" s="12"/>
       <c r="K703" s="13"/>
@@ -33383,7 +33362,7 @@
         <v>31097</v>
       </c>
       <c r="I704" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H704,TODAY(),"Y")</f>
       </c>
       <c r="J704" s="14">
         <v>1</v>
@@ -33425,7 +33404,7 @@
         <v>34830</v>
       </c>
       <c r="I705" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H705,TODAY(),"Y")</f>
       </c>
       <c r="J705" s="14"/>
       <c r="K705" s="11"/>
@@ -33461,7 +33440,7 @@
         <v>44394</v>
       </c>
       <c r="I706" s="9">
-        <f ca="1" t="shared" si="10"/>
+        <f>DATEDIF(H706,TODAY(),"Y")</f>
       </c>
       <c r="J706" s="14"/>
       <c r="K706" s="11"/>
@@ -33497,7 +33476,7 @@
         <v>44911</v>
       </c>
       <c r="I707" s="9">
-        <f ca="1" t="shared" ref="I707" si="11">DATEDIF(H707,TODAY(),"Y")</f>
+        <f>DATEDIF(H707,TODAY(),"Y")</f>
       </c>
       <c r="J707" s="14"/>
       <c r="K707" s="11"/>
@@ -33533,7 +33512,7 @@
         <v>45843</v>
       </c>
       <c r="I708" s="9">
-        <f ca="1" t="shared" ref="I708:I726" si="12">DATEDIF(H708,TODAY(),"Y")</f>
+        <f>DATEDIF(H708,TODAY(),"Y")</f>
       </c>
       <c r="J708" s="14"/>
       <c r="K708" s="11"/>
@@ -33569,7 +33548,7 @@
         <v>33058</v>
       </c>
       <c r="I709" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H709,TODAY(),"Y")</f>
       </c>
       <c r="J709" s="14">
         <v>1</v>
@@ -33611,7 +33590,7 @@
         <v>34861</v>
       </c>
       <c r="I710" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H710,TODAY(),"Y")</f>
       </c>
       <c r="J710" s="14"/>
       <c r="K710" s="11"/>
@@ -33647,7 +33626,7 @@
         <v>42844</v>
       </c>
       <c r="I711" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H711,TODAY(),"Y")</f>
       </c>
       <c r="J711" s="14"/>
       <c r="K711" s="11"/>
@@ -33683,7 +33662,7 @@
         <v>45546</v>
       </c>
       <c r="I712" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H712,TODAY(),"Y")</f>
       </c>
       <c r="J712" s="14"/>
       <c r="K712" s="11"/>
@@ -33719,7 +33698,7 @@
         <v>34369</v>
       </c>
       <c r="I713" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H713,TODAY(),"Y")</f>
       </c>
       <c r="J713" s="14">
         <v>1</v>
@@ -33761,7 +33740,7 @@
         <v>36041</v>
       </c>
       <c r="I714" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H714,TODAY(),"Y")</f>
       </c>
       <c r="J714" s="14"/>
       <c r="K714" s="11"/>
@@ -33799,7 +33778,7 @@
         <v>45873</v>
       </c>
       <c r="I715" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H715,TODAY(),"Y")</f>
       </c>
       <c r="J715" s="14"/>
       <c r="K715" s="11"/>
@@ -33837,7 +33816,7 @@
         <v>33058</v>
       </c>
       <c r="I716" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H716,TODAY(),"Y")</f>
       </c>
       <c r="J716" s="14">
         <v>1</v>
@@ -33879,7 +33858,7 @@
         <v>45097</v>
       </c>
       <c r="I717" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H717,TODAY(),"Y")</f>
       </c>
       <c r="J717" s="14"/>
       <c r="K717" s="11"/>
@@ -33917,7 +33896,7 @@
         <v>44407</v>
       </c>
       <c r="I718" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H718,TODAY(),"Y")</f>
       </c>
       <c r="J718" s="14"/>
       <c r="K718" s="11"/>
@@ -33955,7 +33934,7 @@
         <v>46119</v>
       </c>
       <c r="I719" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H719,TODAY(),"Y")</f>
       </c>
       <c r="J719" s="14"/>
       <c r="K719" s="11"/>
@@ -33993,7 +33972,7 @@
         <v>33877</v>
       </c>
       <c r="I720" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H720,TODAY(),"Y")</f>
       </c>
       <c r="J720" s="14"/>
       <c r="K720" s="11"/>
@@ -34031,7 +34010,7 @@
         <v>31161</v>
       </c>
       <c r="I721" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H721,TODAY(),"Y")</f>
       </c>
       <c r="J721" s="14">
         <v>1</v>
@@ -34073,7 +34052,7 @@
         <v>33863</v>
       </c>
       <c r="I722" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H722,TODAY(),"Y")</f>
       </c>
       <c r="J722" s="14"/>
       <c r="K722" s="11"/>
@@ -34111,7 +34090,7 @@
         <v>42177</v>
       </c>
       <c r="I723" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H723,TODAY(),"Y")</f>
       </c>
       <c r="J723" s="14"/>
       <c r="K723" s="11"/>
@@ -34149,7 +34128,7 @@
         <v>43917</v>
       </c>
       <c r="I724" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H724,TODAY(),"Y")</f>
       </c>
       <c r="J724" s="14"/>
       <c r="K724" s="11"/>
@@ -34187,7 +34166,7 @@
         <v>36995</v>
       </c>
       <c r="I725" s="9">
-        <f ca="1" t="shared" si="12"/>
+        <f>DATEDIF(H725,TODAY(),"Y")</f>
       </c>
       <c r="J725" s="14">
         <v>0</v>
